--- a/outputs/lich_truc_final.xlsx
+++ b/outputs/lich_truc_final.xlsx
@@ -534,7 +534,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>CB011, CB035, CB043, CB070, CB072</t>
+          <t>CB028, CB045, CB052, CB056, CB069</t>
         </is>
       </c>
     </row>
@@ -572,7 +572,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>CB034, CB042, CB052, CB062, CB070</t>
+          <t>CB028, CB045, CB052, CB056, CB069</t>
         </is>
       </c>
     </row>
@@ -610,7 +610,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>CB016, CB022, CB028, CB031, CB035, CB037, CB056, CB063, CB070</t>
+          <t>CB020, CB028, CB045, CB052, CB054, CB056, CB064, CB069, CB073</t>
         </is>
       </c>
     </row>
@@ -648,7 +648,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>CB049, CB052, CB056</t>
+          <t>CB020, CB054, CB073</t>
         </is>
       </c>
     </row>
@@ -686,7 +686,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>CB015, CB026, CB069, CB073</t>
+          <t>CB020, CB022, CB054, CB073</t>
         </is>
       </c>
     </row>
@@ -724,7 +724,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>CB009, CB013, CB040, CB041, CB048, CB051, CB055, CB068, CB071</t>
+          <t>CB006, CB013, CB020, CB022, CB035, CB054, CB058, CB068, CB073</t>
         </is>
       </c>
     </row>
@@ -762,7 +762,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>CB010, CB019, CB039, CB045, CB049, CB050</t>
+          <t>CB020, CB022, CB032, CB050, CB054, CB073</t>
         </is>
       </c>
     </row>
@@ -800,7 +800,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>CB047, CB050, CB064</t>
+          <t>CB022, CB032, CB050</t>
         </is>
       </c>
     </row>
@@ -838,7 +838,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>CB018, CB030, CB046, CB053</t>
+          <t>CB013, CB022, CB032, CB050</t>
         </is>
       </c>
     </row>
@@ -876,7 +876,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>CB069</t>
+          <t>CB035</t>
         </is>
       </c>
     </row>
@@ -914,7 +914,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>CB016</t>
+          <t>CB070</t>
         </is>
       </c>
     </row>
@@ -952,7 +952,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>CB026, CB050, CB062, CB063, CB073</t>
+          <t>CB031, CB049, CB062, CB064, CB070</t>
         </is>
       </c>
     </row>
@@ -990,7 +990,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>CB004, CB023, CB039</t>
+          <t>CB031, CB049, CB064</t>
         </is>
       </c>
     </row>
@@ -1028,7 +1028,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>CB001, CB005, CB024, CB029, CB030, CB036, CB040, CB057, CB065</t>
+          <t>CB006, CB007, CB013, CB038, CB041, CB046, CB055, CB057, CB066</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>CB043</t>
+          <t>CB064</t>
         </is>
       </c>
     </row>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>CB010, CB011, CB020, CB022, CB044, CB050, CB062</t>
+          <t>CB010, CB014, CB031, CB034, CB037, CB049, CB064</t>
         </is>
       </c>
     </row>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>CB023, CB031</t>
+          <t>CB014, CB033</t>
         </is>
       </c>
     </row>
@@ -1180,7 +1180,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>CB006, CB007, CB012, CB013, CB025, CB036, CB060</t>
+          <t>CB006, CB007, CB021, CB029, CB038, CB053, CB055</t>
         </is>
       </c>
     </row>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>CB002, CB028, CB042, CB044, CB047, CB064</t>
+          <t>CB011, CB014, CB033, CB037, CB042, CB043</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1256,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>CB004, CB011, CB015, CB019, CB037, CB043, CB069</t>
+          <t>CB011, CB014, CB033, CB037, CB042, CB043, CB069</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>CB033, CB035, CB044, CB052, CB070</t>
+          <t>CB010, CB011, CB031, CB042, CB043</t>
         </is>
       </c>
     </row>
@@ -1332,7 +1332,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>CB042</t>
+          <t>CB043</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>CB014, CB020, CB052, CB059, CB063, CB069</t>
+          <t>CB042, CB043, CB045, CB047, CB063, CB070</t>
         </is>
       </c>
     </row>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>CB010, CB011, CB016, CB020, CB026, CB031, CB033, CB045, CB069</t>
+          <t>CB010, CB023, CB031, CB042, CB043, CB045, CB047, CB069, CB070</t>
         </is>
       </c>
     </row>
@@ -1446,7 +1446,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>CB019, CB042</t>
+          <t>CB023, CB070</t>
         </is>
       </c>
     </row>
@@ -1484,7 +1484,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>CB073</t>
+          <t>CB067</t>
         </is>
       </c>
     </row>
@@ -1522,7 +1522,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>CB007, CB018, CB030, CB040, CB046, CB055</t>
+          <t>CB001, CB018, CB024, CB036, CB057, CB067</t>
         </is>
       </c>
     </row>
@@ -1560,7 +1560,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>CB006, CB008, CB024, CB057, CB061, CB071</t>
+          <t>CB001, CB018, CB024, CB036, CB057, CB067</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>CB007, CB027, CB030, CB048, CB071</t>
+          <t>CB001, CB018, CB024, CB036, CB057</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>CB003, CB006, CB009, CB018, CB021, CB029, CB060</t>
+          <t>CB001, CB013, CB018, CB024, CB036, CB040, CB057</t>
         </is>
       </c>
     </row>
@@ -1674,7 +1674,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>CB002, CB004, CB016, CB019, CB028, CB034, CB047, CB054, CB072</t>
+          <t>CB012, CB017, CB035, CB045, CB051, CB059, CB060, CB065, CB068</t>
         </is>
       </c>
     </row>
@@ -1712,7 +1712,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>CB009, CB025, CB032, CB051, CB058, CB065, CB066</t>
+          <t>CB012, CB017, CB035, CB051, CB060, CB065, CB068</t>
         </is>
       </c>
     </row>
@@ -1750,7 +1750,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>CB005, CB030, CB061</t>
+          <t>CB012, CB051, CB060</t>
         </is>
       </c>
     </row>
@@ -1788,7 +1788,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>CB017, CB038, CB061</t>
+          <t>CB012, CB051, CB060</t>
         </is>
       </c>
     </row>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>CB001, CB008, CB025, CB027, CB040, CB048, CB061</t>
+          <t>CB006, CB012, CB024, CB025, CB041, CB051, CB060</t>
         </is>
       </c>
     </row>
@@ -1864,7 +1864,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>CB004, CB016, CB031</t>
+          <t>CB004, CB027, CB067</t>
         </is>
       </c>
     </row>
@@ -1902,7 +1902,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>CB006, CB012, CB018, CB021, CB024, CB041, CB046, CB065, CB068</t>
+          <t>CB003, CB004, CB007, CB009, CB017, CB021, CB025, CB027, CB067</t>
         </is>
       </c>
     </row>
@@ -1940,7 +1940,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>CB005, CB017, CB051, CB055, CB060</t>
+          <t>CB007, CB009, CB021, CB025, CB071</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>CB003, CB017, CB021, CB024, CB038, CB065, CB066</t>
+          <t>CB003, CB007, CB009, CB021, CB025, CB038, CB040</t>
         </is>
       </c>
     </row>
@@ -2016,7 +2016,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>CB012</t>
+          <t>CB003</t>
         </is>
       </c>
     </row>
@@ -2054,7 +2054,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>CB060</t>
+          <t>CB003</t>
         </is>
       </c>
     </row>
@@ -2092,7 +2092,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>CB001, CB009, CB025, CB041, CB046, CB053, CB055</t>
+          <t>CB003, CB004, CB009, CB025, CB038, CB058, CB065</t>
         </is>
       </c>
     </row>
@@ -2130,7 +2130,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>CB014, CB034, CB050, CB067</t>
+          <t>CB002, CB016, CB028, CB034</t>
         </is>
       </c>
     </row>
@@ -2168,7 +2168,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>CB032</t>
+          <t>CB061</t>
         </is>
       </c>
     </row>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>CB002, CB015, CB026, CB028, CB037, CB045, CB054, CB070</t>
+          <t>CB010, CB011, CB015, CB016, CB034, CB047, CB061, CB062</t>
         </is>
       </c>
     </row>
@@ -2244,7 +2244,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>CB002, CB016, CB023, CB035, CB044, CB045, CB047, CB064</t>
+          <t>CB010, CB011, CB015, CB016, CB034, CB047, CB061, CB062</t>
         </is>
       </c>
     </row>
@@ -2282,7 +2282,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>CB023, CB033, CB037, CB039, CB063, CB064, CB067</t>
+          <t>CB004, CB017, CB027, CB050, CB061, CB065, CB068</t>
         </is>
       </c>
     </row>
@@ -2320,7 +2320,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>CB034, CB037, CB049</t>
+          <t>CB023, CB037, CB072</t>
         </is>
       </c>
     </row>
@@ -2358,7 +2358,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>CB011, CB022, CB028, CB031, CB039, CB042, CB043, CB044, CB072</t>
+          <t>CB002, CB011, CB015, CB023, CB037, CB039, CB049, CB063, CB072</t>
         </is>
       </c>
     </row>
@@ -2396,7 +2396,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>CB010, CB022, CB033, CB039, CB047, CB049</t>
+          <t>CB015, CB023, CB039, CB049, CB063, CB072</t>
         </is>
       </c>
     </row>
@@ -2434,7 +2434,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>CB009, CB025, CB036, CB038, CB051, CB058, CB066, CB067</t>
+          <t>CB005, CB008, CB018, CB029, CB046, CB048, CB053, CB066</t>
         </is>
       </c>
     </row>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>CB022, CB054, CB062</t>
+          <t>CB015, CB023, CB072</t>
         </is>
       </c>
     </row>
@@ -2510,7 +2510,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>CB013, CB053, CB066, CB071</t>
+          <t>CB005, CB030, CB046, CB048</t>
         </is>
       </c>
     </row>
@@ -2548,7 +2548,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>CB032</t>
+          <t>CB001</t>
         </is>
       </c>
     </row>
@@ -2586,7 +2586,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>CB014, CB034, CB035, CB044, CB059</t>
+          <t>CB015, CB031, CB033, CB044, CB062</t>
         </is>
       </c>
     </row>
@@ -2624,7 +2624,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>CB003, CB005, CB021, CB048, CB067</t>
+          <t>CB013, CB027, CB036, CB040, CB041</t>
         </is>
       </c>
     </row>
@@ -2662,7 +2662,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>CB034, CB039, CB045, CB059</t>
+          <t>CB002, CB044, CB059, CB063</t>
         </is>
       </c>
     </row>
@@ -2700,7 +2700,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>CB056, CB059</t>
+          <t>CB002, CB059</t>
         </is>
       </c>
     </row>
@@ -2738,7 +2738,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>CB002, CB011, CB019, CB023, CB031, CB043, CB049, CB059</t>
+          <t>CB002, CB016, CB019, CB026, CB034, CB039, CB056, CB059</t>
         </is>
       </c>
     </row>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>CB054, CB064, CB072, CB073</t>
+          <t>CB016, CB019, CB026, CB056</t>
         </is>
       </c>
     </row>
@@ -2814,7 +2814,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>CB010, CB015, CB063</t>
+          <t>CB019, CB026, CB039</t>
         </is>
       </c>
     </row>
@@ -2852,7 +2852,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>CB019, CB052, CB056, CB064</t>
+          <t>CB019, CB026, CB032, CB039</t>
         </is>
       </c>
     </row>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>CB001, CB007, CB012, CB017, CB038, CB055, CB057, CB058</t>
+          <t>CB008, CB009, CB040, CB041, CB053, CB055, CB058, CB071</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>CB014</t>
+          <t>CB019</t>
         </is>
       </c>
     </row>
@@ -2966,7 +2966,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>CB009, CB017, CB024, CB036, CB040, CB041, CB046, CB053, CB071</t>
+          <t>CB008, CB009, CB029, CB040, CB041, CB053, CB055, CB058, CB071</t>
         </is>
       </c>
     </row>
@@ -3004,7 +3004,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>CB026, CB028, CB033, CB042, CB056, CB072</t>
+          <t>CB019, CB026, CB028, CB037, CB047, CB072</t>
         </is>
       </c>
     </row>
@@ -3042,7 +3042,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>CB060</t>
+          <t>CB055</t>
         </is>
       </c>
     </row>
@@ -3080,7 +3080,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>CB015</t>
+          <t>CB047</t>
         </is>
       </c>
     </row>
@@ -3118,7 +3118,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>CB003, CB008, CB018, CB029, CB038, CB046, CB057, CB065</t>
+          <t>CB004, CB017, CB027, CB050, CB061, CB065, CB066, CB068</t>
         </is>
       </c>
     </row>
@@ -3156,7 +3156,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>CB058, CB066</t>
+          <t>CB008, CB030</t>
         </is>
       </c>
     </row>
@@ -3194,7 +3194,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>CB001, CB027, CB068</t>
+          <t>CB008, CB030, CB066</t>
         </is>
       </c>
     </row>
@@ -3232,7 +3232,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>CB005, CB008, CB018, CB027, CB029, CB032, CB053, CB067, CB068</t>
+          <t>CB005, CB008, CB018, CB029, CB030, CB046, CB048, CB053, CB066</t>
         </is>
       </c>
     </row>
@@ -3270,7 +3270,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>CB006, CB013, CB021, CB027, CB036</t>
+          <t>CB005, CB006, CB029, CB046, CB048</t>
         </is>
       </c>
     </row>
@@ -3308,7 +3308,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>CB003, CB008, CB012, CB029, CB051, CB068</t>
+          <t>CB005, CB006, CB007, CB029, CB046, CB048</t>
         </is>
       </c>
     </row>
@@ -3346,7 +3346,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>CB014, CB062, CB073</t>
+          <t>CB014, CB044, CB062</t>
         </is>
       </c>
     </row>
@@ -3384,7 +3384,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>CB047, CB054</t>
+          <t>CB044, CB062</t>
         </is>
       </c>
     </row>
@@ -3422,7 +3422,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>CB004, CB020</t>
+          <t>CB044, CB052</t>
         </is>
       </c>
     </row>
@@ -3460,7 +3460,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>CB002, CB015, CB020, CB023, CB028, CB043, CB045, CB062, CB063</t>
+          <t>CB002, CB016, CB028, CB033, CB034, CB044, CB052, CB059, CB063</t>
         </is>
       </c>
     </row>
@@ -3498,7 +3498,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>CB041</t>
+          <t>CB071</t>
         </is>
       </c>
     </row>
@@ -3536,7 +3536,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>CB007, CB013, CB032, CB048, CB057, CB058, CB061</t>
+          <t>CB021, CB030, CB032, CB038, CB057, CB058, CB071</t>
         </is>
       </c>
     </row>
@@ -3619,7 +3619,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>20260528_3 (Cơ sở 2), 20260602_4 (Cơ sở 2), 20260604_2 (Cơ sở 2), 20260613_2 (Cơ sở 2), 20260608_3 (Cơ sở 2)</t>
+          <t>20260601_1 (Cơ sở 2), 20260601_2 (Cơ sở 2), 20260601_3 (Cơ sở 2), 20260601_4 (Cơ sở 2), 20260610_3 (Cơ sở 2)</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -3648,7 +3648,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>20260529_1 (Cơ sở 1), 20260601_5 (Cơ sở 1), 20260605_2 (Cơ sở 1), 20260605_3 (Cơ sở 1), 20260612_2 (Cơ sở 1), 20260611_1 (Cơ sở 1)</t>
+          <t>20260604_2 (Cơ sở 1), 20260608_3 (Cơ sở 1), 20260611_3 (Cơ sở 1), 20260612_1 (Cơ sở 1), 20260612_2 (Cơ sở 1), 20260611_1 (Cơ sở 1)</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -3677,7 +3677,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>20260601_4 (Cơ sở 2), 20260603_3 (Cơ sở 2), 20260611_3 (Cơ sở 2), 20260608_1 (Cơ sở 2), 20260610_1 (Cơ sở 2)</t>
+          <t>20260603_1 (Cơ sở 2), 20260603_3 (Cơ sở 2), 20260603_4 (Cơ sở 2), 20260604_1 (Cơ sở 2), 20260604_2 (Cơ sở 2)</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>20260528_2 (Cơ sở 1), 20260529_2 (Cơ sở 1), 20260601_5 (Cơ sở 1), 20260602_5 (Cơ sở 1), 20260610_4 (Cơ sở 1)</t>
+          <t>20260602_5 (Cơ sở 1), 20260603_1 (Cơ sở 2), 20260604_2 (Cơ sở 2), 20260605_4 (Cơ sở 1), 20260608_1 (Cơ sở 2)</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -3735,7 +3735,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>20260528_3 (Cơ sở 2), 20260602_2 (Cơ sở 2), 20260603_2 (Cơ sở 2), 20260611_3 (Cơ sở 2), 20260608_4 (Cơ sở 2)</t>
+          <t>20260609_2 (Cơ sở 2), 20260609_3 (Cơ sở 2), 20260608_4 (Cơ sở 2), 20260609_4 (Cơ sở 2), 20260610_1 (Cơ sở 2)</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -3760,11 +3760,11 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>20260529_1 (Cơ sở 2), 20260601_2 (Cơ sở 2), 20260601_4 (Cơ sở 2), 20260603_1 (Cơ sở 2), 20260609_4 (Cơ sở 2)</t>
+          <t>20260525_2 (Cơ sở 2), 20260528_3 (Cơ sở 2), 20260529_1 (Cơ sở 2), 20260602_4 (Cơ sở 2), 20260609_4 (Cơ sở 2), 20260610_1 (Cơ sở 2)</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -3789,11 +3789,11 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>20260529_1 (Cơ sở 2), 20260601_1 (Cơ sở 2), 20260601_3 (Cơ sở 2), 20260613_2 (Cơ sở 2), 20260612_4 (Cơ sở 2)</t>
+          <t>20260528_3 (Cơ sở 2), 20260529_1 (Cơ sở 2), 20260603_1 (Cơ sở 2), 20260603_2 (Cơ sở 2), 20260603_3 (Cơ sở 2), 20260610_1 (Cơ sở 2)</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -3818,11 +3818,11 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>20260601_2 (Cơ sở 2), 20260602_4 (Cơ sở 2), 20260608_1 (Cơ sở 2), 20260608_4 (Cơ sở 2), 20260610_1 (Cơ sở 2)</t>
+          <t>20260609_2 (Cơ sở 2), 20260613_2 (Cơ sở 2), 20260613_3 (Cơ sở 2), 20260608_2 (Cơ sở 2), 20260608_3 (Cơ sở 2), 20260608_4 (Cơ sở 2)</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -3851,7 +3851,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>20260525_2 (Cơ sở 2), 20260601_4 (Cơ sở 2), 20260602_1 (Cơ sở 2), 20260604_2 (Cơ sở 2), 20260609_2 (Cơ sở 2), 20260613_3 (Cơ sở 2)</t>
+          <t>20260603_1 (Cơ sở 2), 20260603_2 (Cơ sở 2), 20260603_3 (Cơ sở 2), 20260604_2 (Cơ sở 2), 20260613_2 (Cơ sở 2), 20260613_3 (Cơ sở 2)</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -3880,7 +3880,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>20260525_5 (Cơ sở 1), 20260528_4 (Cơ sở 1), 20260530_3 (Cơ sở 1), 20260608_4 (Cơ sở 1), 20260612_4 (Cơ sở 1)</t>
+          <t>20260528_4 (Cơ sở 1), 20260529_3 (Cơ sở 1), 20260530_3 (Cơ sở 1), 20260605_2 (Cơ sở 1), 20260605_3 (Cơ sở 1)</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -3909,7 +3909,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>20260518_5 (Cơ sở 1), 20260528_4 (Cơ sở 1), 20260529_2 (Cơ sở 1), 20260530_3 (Cơ sở 1), 20260608_3 (Cơ sở 1), 20260612_2 (Cơ sở 1)</t>
+          <t>20260529_1 (Cơ sở 1), 20260529_2 (Cơ sở 1), 20260529_3 (Cơ sở 1), 20260605_2 (Cơ sở 1), 20260605_3 (Cơ sở 1), 20260608_3 (Cơ sở 1)</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -3938,7 +3938,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>20260529_1 (Cơ sở 2), 20260603_1 (Cơ sở 2), 20260603_4 (Cơ sở 2), 20260613_2 (Cơ sở 2), 20260610_1 (Cơ sở 2)</t>
+          <t>20260601_5 (Cơ sở 1), 20260602_1 (Cơ sở 2), 20260602_2 (Cơ sở 2), 20260602_3 (Cơ sở 2), 20260602_4 (Cơ sở 2)</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -3967,7 +3967,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>20260525_2 (Cơ sở 2), 20260529_1 (Cơ sở 2), 20260609_3 (Cơ sở 2), 20260609_4 (Cơ sở 2), 20260612_4 (Cơ sở 2)</t>
+          <t>20260525_2 (Cơ sở 2), 20260527_2 (Cơ sở 2), 20260528_3 (Cơ sở 2), 20260601_4 (Cơ sở 2), 20260611_3 (Cơ sở 2)</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>20260530_2 (Cơ sở 1), 20260604_2 (Cơ sở 1), 20260610_3 (Cơ sở 1), 20260613_2 (Cơ sở 1), 20260610_1 (Cơ sở 1)</t>
+          <t>20260528_4 (Cơ sở 1), 20260528_5 (Cơ sở 1), 20260529_1 (Cơ sở 1), 20260529_2 (Cơ sở 1), 20260610_1 (Cơ sở 1)</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -4025,7 +4025,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>20260523_3 (Cơ sở 1), 20260529_2 (Cơ sở 1), 20260605_2 (Cơ sở 1), 20260612_4 (Cơ sở 1), 20260613_4 (Cơ sở 1), 20260611_1 (Cơ sở 1)</t>
+          <t>20260605_2 (Cơ sở 1), 20260605_3 (Cơ sở 1), 20260608_3 (Cơ sở 1), 20260608_4 (Cơ sở 1), 20260609_2 (Cơ sở 1), 20260610_3 (Cơ sở 1)</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -4054,7 +4054,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>20260521_5 (Cơ sở 1), 20260527_5 (Cơ sở 1), 20260530_3 (Cơ sở 1), 20260601_5 (Cơ sở 1), 20260602_5 (Cơ sở 1), 20260605_3 (Cơ sở 1)</t>
+          <t>20260604_2 (Cơ sở 1), 20260605_2 (Cơ sở 1), 20260605_3 (Cơ sở 1), 20260612_2 (Cơ sở 1), 20260612_3 (Cơ sở 1), 20260611_1 (Cơ sở 1)</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -4083,7 +4083,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>20260602_3 (Cơ sở 2), 20260603_2 (Cơ sở 2), 20260603_3 (Cơ sở 2), 20260613_2 (Cơ sở 2), 20260613_3 (Cơ sở 2)</t>
+          <t>20260601_5 (Cơ sở 1), 20260602_1 (Cơ sở 2), 20260603_1 (Cơ sở 2), 20260605_4 (Cơ sở 1), 20260608_1 (Cơ sở 2)</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -4112,7 +4112,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>20260527_2 (Cơ sở 2), 20260601_1 (Cơ sở 2), 20260601_4 (Cơ sở 2), 20260603_1 (Cơ sở 2), 20260608_1 (Cơ sở 2), 20260608_4 (Cơ sở 2)</t>
+          <t>20260601_1 (Cơ sở 2), 20260601_2 (Cơ sở 2), 20260601_3 (Cơ sở 2), 20260601_4 (Cơ sở 2), 20260609_2 (Cơ sở 2), 20260608_4 (Cơ sở 2)</t>
         </is>
       </c>
       <c r="F19" t="n">
@@ -4141,7 +4141,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>20260525_5 (Cơ sở 1), 20260529_2 (Cơ sở 1), 20260531_2 (Cơ sở 1), 20260601_5 (Cơ sở 1), 20260612_2 (Cơ sở 1), 20260613_1 (Cơ sở 1)</t>
+          <t>20260612_2 (Cơ sở 1), 20260612_3 (Cơ sở 1), 20260612_4 (Cơ sở 1), 20260613_1 (Cơ sở 1), 20260613_2 (Cơ sở 1), 20260613_3 (Cơ sở 1)</t>
         </is>
       </c>
       <c r="F20" t="n">
@@ -4170,7 +4170,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>20260528_4 (Cơ sở 1), 20260530_2 (Cơ sở 1), 20260530_3 (Cơ sở 1), 20260610_4 (Cơ sở 1), 20260611_1 (Cơ sở 1)</t>
+          <t>20260521_5 (Cơ sở 1), 20260522_5 (Cơ sở 1), 20260523_3 (Cơ sở 1), 20260525_2 (Cơ sở 2), 20260525_5 (Cơ sở 1)</t>
         </is>
       </c>
       <c r="F21" t="n">
@@ -4199,7 +4199,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>20260601_4 (Cơ sở 2), 20260603_1 (Cơ sở 2), 20260603_3 (Cơ sở 2), 20260611_3 (Cơ sở 2), 20260609_4 (Cơ sở 2)</t>
+          <t>20260529_1 (Cơ sở 2), 20260603_1 (Cơ sở 2), 20260603_2 (Cơ sở 2), 20260603_3 (Cơ sở 2), 20260612_4 (Cơ sở 2)</t>
         </is>
       </c>
       <c r="F22" t="n">
@@ -4228,7 +4228,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>20260521_5 (Cơ sở 1), 20260528_4 (Cơ sở 1), 20260608_3 (Cơ sở 1), 20260608_4 (Cơ sở 1), 20260609_2 (Cơ sở 1)</t>
+          <t>20260523_3 (Cơ sở 1), 20260525_2 (Cơ sở 2), 20260525_5 (Cơ sở 1), 20260526_5 (Cơ sở 1), 20260527_2 (Cơ sở 2)</t>
         </is>
       </c>
       <c r="F23" t="n">
@@ -4257,7 +4257,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>20260528_2 (Cơ sở 1), 20260528_5 (Cơ sở 1), 20260605_3 (Cơ sở 1), 20260605_4 (Cơ sở 1), 20260612_2 (Cơ sở 1), 20260611_1 (Cơ sở 1)</t>
+          <t>20260530_3 (Cơ sở 1), 20260531_2 (Cơ sở 1), 20260608_2 (Cơ sở 1), 20260608_3 (Cơ sở 1), 20260608_4 (Cơ sở 1), 20260609_2 (Cơ sở 1)</t>
         </is>
       </c>
       <c r="F24" t="n">
@@ -4286,7 +4286,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>20260528_3 (Cơ sở 2), 20260601_2 (Cơ sở 2), 20260603_1 (Cơ sở 2), 20260603_3 (Cơ sở 2), 20260613_3 (Cơ sở 2)</t>
+          <t>20260601_1 (Cơ sở 2), 20260601_2 (Cơ sở 2), 20260601_3 (Cơ sở 2), 20260601_4 (Cơ sở 2), 20260602_4 (Cơ sở 2)</t>
         </is>
       </c>
       <c r="F25" t="n">
@@ -4315,7 +4315,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>20260529_1 (Cơ sở 2), 20260602_1 (Cơ sở 2), 20260602_4 (Cơ sở 2), 20260604_2 (Cơ sở 2), 20260609_2 (Cơ sở 2)</t>
+          <t>20260602_4 (Cơ sở 2), 20260603_1 (Cơ sở 2), 20260603_2 (Cơ sở 2), 20260603_3 (Cơ sở 2), 20260604_2 (Cơ sở 2)</t>
         </is>
       </c>
       <c r="F26" t="n">
@@ -4344,7 +4344,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>20260523_3 (Cơ sở 1), 20260528_1 (Cơ sở 1), 20260530_3 (Cơ sở 1), 20260605_2 (Cơ sở 1), 20260613_3 (Cơ sở 1)</t>
+          <t>20260612_2 (Cơ sở 1), 20260612_3 (Cơ sở 1), 20260612_4 (Cơ sở 1), 20260613_1 (Cơ sở 1), 20260613_3 (Cơ sở 1)</t>
         </is>
       </c>
       <c r="F27" t="n">
@@ -4373,7 +4373,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>20260601_3 (Cơ sở 2), 20260602_4 (Cơ sở 2), 20260608_3 (Cơ sở 2), 20260608_4 (Cơ sở 2), 20260609_4 (Cơ sở 2)</t>
+          <t>20260602_5 (Cơ sở 1), 20260603_1 (Cơ sở 2), 20260605_4 (Cơ sở 1), 20260611_3 (Cơ sở 2), 20260608_1 (Cơ sở 2)</t>
         </is>
       </c>
       <c r="F28" t="n">
@@ -4398,11 +4398,11 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>20260521_5 (Cơ sở 1), 20260529_1 (Cơ sở 1), 20260601_5 (Cơ sở 1), 20260605_2 (Cơ sở 1), 20260608_3 (Cơ sở 1), 20260613_3 (Cơ sở 1), 20260611_1 (Cơ sở 1)</t>
+          <t>20260518_5 (Cơ sở 1), 20260519_5 (Cơ sở 1), 20260521_5 (Cơ sở 1), 20260604_2 (Cơ sở 1), 20260613_3 (Cơ sở 1), 20260611_1 (Cơ sở 1)</t>
         </is>
       </c>
       <c r="F29" t="n">
@@ -4427,11 +4427,11 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>20260528_3 (Cơ sở 2), 20260601_4 (Cơ sở 2), 20260608_1 (Cơ sở 2), 20260608_4 (Cơ sở 2), 20260610_1 (Cơ sở 2)</t>
+          <t>20260529_1 (Cơ sở 2), 20260609_2 (Cơ sở 2), 20260613_3 (Cơ sở 2), 20260608_4 (Cơ sở 2), 20260609_4 (Cơ sở 2), 20260610_1 (Cơ sở 2)</t>
         </is>
       </c>
       <c r="F30" t="n">
@@ -4460,7 +4460,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>20260527_2 (Cơ sở 2), 20260528_3 (Cơ sở 2), 20260601_1 (Cơ sở 2), 20260601_3 (Cơ sở 2), 20260602_2 (Cơ sở 2)</t>
+          <t>20260609_3 (Cơ sở 2), 20260608_2 (Cơ sở 2), 20260608_3 (Cơ sở 2), 20260608_4 (Cơ sở 2), 20260612_4 (Cơ sở 2)</t>
         </is>
       </c>
       <c r="F31" t="n">
@@ -4489,7 +4489,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>20260521_5 (Cơ sở 1), 20260528_5 (Cơ sở 1), 20260530_3 (Cơ sở 1), 20260602_5 (Cơ sở 1), 20260608_3 (Cơ sở 1), 20260612_2 (Cơ sở 1)</t>
+          <t>20260528_1 (Cơ sở 1), 20260528_2 (Cơ sở 1), 20260528_4 (Cơ sở 1), 20260529_3 (Cơ sở 1), 20260530_3 (Cơ sở 1), 20260610_3 (Cơ sở 1)</t>
         </is>
       </c>
       <c r="F32" t="n">
@@ -4518,7 +4518,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>20260602_1 (Cơ sở 2), 20260604_3 (Cơ sở 2), 20260610_3 (Cơ sở 2), 20260608_4 (Cơ sở 2), 20260612_4 (Cơ sở 2)</t>
+          <t>20260525_5 (Cơ sở 1), 20260526_5 (Cơ sở 1), 20260527_2 (Cơ sở 2), 20260613_1 (Cơ sở 1), 20260612_4 (Cơ sở 2)</t>
         </is>
       </c>
       <c r="F33" t="n">
@@ -4547,7 +4547,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>20260529_3 (Cơ sở 1), 20260530_3 (Cơ sở 1), 20260605_4 (Cơ sở 1), 20260608_4 (Cơ sở 1), 20260613_3 (Cơ sở 1)</t>
+          <t>20260528_5 (Cơ sở 1), 20260529_1 (Cơ sở 1), 20260529_2 (Cơ sở 1), 20260610_3 (Cơ sở 1), 20260611_1 (Cơ sở 1)</t>
         </is>
       </c>
       <c r="F34" t="n">
@@ -4576,7 +4576,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>20260519_5 (Cơ sở 1), 20260601_5 (Cơ sở 1), 20260604_2 (Cơ sở 1), 20260608_2 (Cơ sở 1), 20260610_3 (Cơ sở 1), 20260611_3 (Cơ sở 1)</t>
+          <t>20260528_4 (Cơ sở 1), 20260604_2 (Cơ sở 1), 20260605_2 (Cơ sở 1), 20260605_3 (Cơ sở 1), 20260612_2 (Cơ sở 1), 20260611_1 (Cơ sở 1)</t>
         </is>
       </c>
       <c r="F35" t="n">
@@ -4601,11 +4601,11 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>20260518_5 (Cơ sở 1), 20260521_5 (Cơ sở 1), 20260529_3 (Cơ sở 1), 20260605_3 (Cơ sở 1), 20260610_3 (Cơ sở 1)</t>
+          <t>20260525_2 (Cơ sở 2), 20260527_4 (Cơ sở 1), 20260601_5 (Cơ sở 1), 20260602_1 (Cơ sở 2)</t>
         </is>
       </c>
       <c r="F36" t="n">
@@ -4634,7 +4634,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>20260528_3 (Cơ sở 2), 20260529_1 (Cơ sở 2), 20260609_2 (Cơ sở 2), 20260613_3 (Cơ sở 2), 20260609_4 (Cơ sở 2)</t>
+          <t>20260601_1 (Cơ sở 2), 20260601_2 (Cơ sở 2), 20260601_3 (Cơ sở 2), 20260601_4 (Cơ sở 2), 20260611_3 (Cơ sở 2)</t>
         </is>
       </c>
       <c r="F37" t="n">
@@ -4659,11 +4659,11 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>20260521_5 (Cơ sở 1), 20260529_2 (Cơ sở 1), 20260605_2 (Cơ sở 1), 20260605_4 (Cơ sở 1), 20260608_2 (Cơ sở 1)</t>
+          <t>20260528_4 (Cơ sở 1), 20260529_1 (Cơ sở 1), 20260529_2 (Cơ sở 1), 20260608_2 (Cơ sở 1), 20260608_3 (Cơ sở 1), 20260613_3 (Cơ sở 1)</t>
         </is>
       </c>
       <c r="F38" t="n">
@@ -4692,7 +4692,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>20260602_3 (Cơ sở 2), 20260603_3 (Cơ sở 2), 20260609_2 (Cơ sở 2), 20260613_2 (Cơ sở 2), 20260608_1 (Cơ sở 2)</t>
+          <t>20260528_3 (Cơ sở 2), 20260529_1 (Cơ sở 2), 20260603_3 (Cơ sở 2), 20260604_2 (Cơ sở 2), 20260612_4 (Cơ sở 2)</t>
         </is>
       </c>
       <c r="F39" t="n">
@@ -4717,11 +4717,11 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>20260525_5 (Cơ sở 1), 20260528_2 (Cơ sở 1), 20260605_4 (Cơ sở 1), 20260608_3 (Cơ sở 1), 20260608_4 (Cơ sở 1), 20260611_3 (Cơ sở 1)</t>
+          <t>20260608_3 (Cơ sở 1), 20260608_4 (Cơ sở 1), 20260612_2 (Cơ sở 1), 20260612_4 (Cơ sở 1), 20260613_1 (Cơ sở 1)</t>
         </is>
       </c>
       <c r="F40" t="n">
@@ -4750,7 +4750,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>20260525_2 (Cơ sở 2), 20260528_3 (Cơ sở 2), 20260601_1 (Cơ sở 2), 20260602_4 (Cơ sở 2), 20260613_3 (Cơ sở 2)</t>
+          <t>20260601_4 (Cơ sở 2), 20260603_3 (Cơ sở 2), 20260611_3 (Cơ sở 2), 20260613_2 (Cơ sở 2), 20260613_3 (Cơ sở 2)</t>
         </is>
       </c>
       <c r="F41" t="n">
@@ -4779,7 +4779,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>20260525_2 (Cơ sở 2), 20260603_1 (Cơ sở 2), 20260604_2 (Cơ sở 2), 20260613_3 (Cơ sở 2), 20260612_3 (Cơ sở 2)</t>
+          <t>20260528_3 (Cơ sở 2), 20260602_4 (Cơ sở 2), 20260611_3 (Cơ sở 2), 20260613_2 (Cơ sở 2), 20260613_3 (Cơ sở 2)</t>
         </is>
       </c>
       <c r="F42" t="n">
@@ -4804,11 +4804,11 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>20260519_5 (Cơ sở 1), 20260529_1 (Cơ sở 1), 20260529_5 (Cơ sở 1), 20260531_2 (Cơ sở 1), 20260608_3 (Cơ sở 1), 20260613_3 (Cơ sở 1)</t>
+          <t>20260529_1 (Cơ sở 1), 20260529_2 (Cơ sở 1), 20260529_3 (Cơ sở 1), 20260530_2 (Cơ sở 1), 20260530_3 (Cơ sở 1)</t>
         </is>
       </c>
       <c r="F43" t="n">
@@ -4837,7 +4837,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>20260518_5 (Cơ sở 1), 20260528_3 (Cơ sở 1), 20260529_2 (Cơ sở 1), 20260608_3 (Cơ sở 1), 20260612_2 (Cơ sở 1), 20260611_1 (Cơ sở 1)</t>
+          <t>20260529_1 (Cơ sở 1), 20260529_2 (Cơ sở 1), 20260529_3 (Cơ sở 1), 20260529_5 (Cơ sở 1), 20260530_2 (Cơ sở 1), 20260530_3 (Cơ sở 1)</t>
         </is>
       </c>
       <c r="F44" t="n">
@@ -4866,7 +4866,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>20260528_4 (Cơ sở 1), 20260529_1 (Cơ sở 1), 20260529_3 (Cơ sở 1), 20260605_3 (Cơ sở 1), 20260608_3 (Cơ sở 1), 20260610_3 (Cơ sở 1)</t>
+          <t>20260610_3 (Cơ sở 1), 20260611_3 (Cơ sở 1), 20260610_1 (Cơ sở 1), 20260610_2 (Cơ sở 1), 20260610_4 (Cơ sở 1), 20260611_1 (Cơ sở 1)</t>
         </is>
       </c>
       <c r="F45" t="n">
@@ -4895,7 +4895,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>20260525_5 (Cơ sở 1), 20260530_3 (Cơ sở 1), 20260605_2 (Cơ sở 1), 20260605_3 (Cơ sở 1), 20260611_3 (Cơ sở 1), 20260611_1 (Cơ sở 1)</t>
+          <t>20260518_5 (Cơ sở 1), 20260519_5 (Cơ sở 1), 20260521_5 (Cơ sở 1), 20260530_2 (Cơ sở 1), 20260530_3 (Cơ sở 1), 20260601_5 (Cơ sở 1)</t>
         </is>
       </c>
       <c r="F46" t="n">
@@ -4924,7 +4924,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>20260527_2 (Cơ sở 2), 20260601_1 (Cơ sở 2), 20260603_1 (Cơ sở 2), 20260604_2 (Cơ sở 2), 20260613_3 (Cơ sở 2), 20260608_1 (Cơ sở 2)</t>
+          <t>20260528_3 (Cơ sở 2), 20260609_2 (Cơ sở 2), 20260609_3 (Cơ sở 2), 20260608_4 (Cơ sở 2), 20260609_4 (Cơ sở 2), 20260610_1 (Cơ sở 2)</t>
         </is>
       </c>
       <c r="F47" t="n">
@@ -4953,7 +4953,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>20260526_5 (Cơ sở 1), 20260529_1 (Cơ sở 1), 20260601_5 (Cơ sở 1), 20260605_3 (Cơ sở 1), 20260608_4 (Cơ sở 1), 20260610_2 (Cơ sở 1)</t>
+          <t>20260530_2 (Cơ sở 1), 20260530_3 (Cơ sở 1), 20260605_2 (Cơ sở 1), 20260605_3 (Cơ sở 1), 20260613_3 (Cơ sở 1), 20260613_4 (Cơ sở 1)</t>
         </is>
       </c>
       <c r="F48" t="n">
@@ -4982,7 +4982,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>20260525_2 (Cơ sở 2), 20260601_3 (Cơ sở 2), 20260602_4 (Cơ sở 2), 20260611_3 (Cơ sở 2), 20260612_4 (Cơ sở 2)</t>
+          <t>20260609_2 (Cơ sở 2), 20260609_3 (Cơ sở 2), 20260608_4 (Cơ sở 2), 20260609_4 (Cơ sở 2), 20260610_1 (Cơ sở 2)</t>
         </is>
       </c>
       <c r="F49" t="n">
@@ -5011,7 +5011,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>20260522_5 (Cơ sở 1), 20260525_5 (Cơ sở 1), 20260608_2 (Cơ sở 1), 20260608_4 (Cơ sở 1), 20260612_2 (Cơ sở 1)</t>
+          <t>20260528_1 (Cơ sở 1), 20260528_2 (Cơ sở 1), 20260528_4 (Cơ sở 1), 20260608_3 (Cơ sở 1), 20260608_4 (Cơ sở 1)</t>
         </is>
       </c>
       <c r="F50" t="n">
@@ -5040,7 +5040,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>20260525_5 (Cơ sở 1), 20260526_5 (Cơ sở 1), 20260528_1 (Cơ sở 1), 20260528_4 (Cơ sở 1), 20260604_2 (Cơ sở 1)</t>
+          <t>20260525_5 (Cơ sở 1), 20260526_5 (Cơ sở 1), 20260527_2 (Cơ sở 2), 20260605_4 (Cơ sở 1), 20260608_1 (Cơ sở 2)</t>
         </is>
       </c>
       <c r="F51" t="n">
@@ -5069,7 +5069,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>20260525_2 (Cơ sở 2), 20260602_1 (Cơ sở 2), 20260603_2 (Cơ sở 2), 20260609_2 (Cơ sở 2), 20260610_1 (Cơ sở 2)</t>
+          <t>20260601_5 (Cơ sở 1), 20260602_1 (Cơ sở 2), 20260602_2 (Cơ sở 2), 20260602_3 (Cơ sở 2), 20260602_4 (Cơ sở 2)</t>
         </is>
       </c>
       <c r="F52" t="n">
@@ -5098,7 +5098,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>20260519_5 (Cơ sở 1), 20260522_5 (Cơ sở 1), 20260529_3 (Cơ sở 1), 20260530_2 (Cơ sở 1), 20260613_1 (Cơ sở 1)</t>
+          <t>20260518_5 (Cơ sở 1), 20260519_5 (Cơ sở 1), 20260521_5 (Cơ sở 1), 20260610_4 (Cơ sở 1), 20260611_1 (Cơ sở 1)</t>
         </is>
       </c>
       <c r="F53" t="n">
@@ -5127,7 +5127,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>20260527_2 (Cơ sở 2), 20260604_2 (Cơ sở 2), 20260609_3 (Cơ sở 2), 20260613_3 (Cơ sở 2), 20260608_4 (Cơ sở 2)</t>
+          <t>20260529_1 (Cơ sở 2), 20260609_2 (Cơ sở 2), 20260613_2 (Cơ sở 2), 20260613_3 (Cơ sở 2), 20260608_4 (Cơ sở 2)</t>
         </is>
       </c>
       <c r="F54" t="n">
@@ -5156,7 +5156,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>20260601_5 (Cơ sở 1), 20260605_2 (Cơ sở 1), 20260609_2 (Cơ sở 1), 20260612_3 (Cơ sở 1), 20260610_2 (Cơ sở 1)</t>
+          <t>20260521_5 (Cơ sở 1), 20260522_5 (Cơ sở 1), 20260523_3 (Cơ sở 1), 20260525_2 (Cơ sở 2), 20260525_5 (Cơ sở 1)</t>
         </is>
       </c>
       <c r="F55" t="n">
@@ -5185,7 +5185,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>20260525_2 (Cơ sở 2), 20260601_1 (Cơ sở 2), 20260603_2 (Cơ sở 2), 20260604_2 (Cơ sở 2), 20260613_2 (Cơ sở 2)</t>
+          <t>20260528_3 (Cơ sở 2), 20260529_1 (Cơ sở 2), 20260613_2 (Cơ sở 2), 20260613_3 (Cơ sở 2), 20260613_4 (Cơ sở 2)</t>
         </is>
       </c>
       <c r="F56" t="n">
@@ -5214,7 +5214,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>20260521_5 (Cơ sở 1), 20260522_5 (Cơ sở 1), 20260612_1 (Cơ sở 1), 20260613_1 (Cơ sở 1), 20260613_3 (Cơ sở 1)</t>
+          <t>20260518_5 (Cơ sở 1), 20260519_5 (Cơ sở 1), 20260521_5 (Cơ sở 1), 20260612_2 (Cơ sở 1), 20260612_3 (Cơ sở 1)</t>
         </is>
       </c>
       <c r="F57" t="n">
@@ -5239,11 +5239,11 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>20260528_3 (Cơ sở 2), 20260601_2 (Cơ sở 2), 20260613_2 (Cơ sở 2), 20260608_1 (Cơ sở 2), 20260612_4 (Cơ sở 2)</t>
+          <t>20260528_3 (Cơ sở 2), 20260601_1 (Cơ sở 2), 20260601_2 (Cơ sở 2), 20260601_3 (Cơ sở 2), 20260601_4 (Cơ sở 2), 20260612_4 (Cơ sở 2)</t>
         </is>
       </c>
       <c r="F58" t="n">
@@ -5272,7 +5272,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>20260602_1 (Cơ sở 2), 20260609_2 (Cơ sở 2), 20260613_2 (Cơ sở 2), 20260608_2 (Cơ sở 2), 20260612_4 (Cơ sở 2)</t>
+          <t>20260525_2 (Cơ sở 2), 20260604_2 (Cơ sở 2), 20260613_2 (Cơ sở 2), 20260613_3 (Cơ sở 2), 20260612_4 (Cơ sở 2)</t>
         </is>
       </c>
       <c r="F59" t="n">
@@ -5301,7 +5301,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>20260530_2 (Cơ sở 1), 20260610_3 (Cơ sở 1), 20260611_3 (Cơ sở 1), 20260612_1 (Cơ sở 1), 20260612_2 (Cơ sở 1)</t>
+          <t>20260601_5 (Cơ sở 1), 20260611_3 (Cơ sở 1), 20260612_1 (Cơ sở 1), 20260612_2 (Cơ sở 1), 20260611_1 (Cơ sở 1)</t>
         </is>
       </c>
       <c r="F60" t="n">
@@ -5330,7 +5330,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>20260529_1 (Cơ sở 2), 20260601_4 (Cơ sở 2), 20260603_2 (Cơ sở 2), 20260604_1 (Cơ sở 2), 20260613_4 (Cơ sở 2)</t>
+          <t>20260601_5 (Cơ sở 1), 20260602_1 (Cơ sở 2), 20260602_2 (Cơ sở 2), 20260602_3 (Cơ sở 2), 20260602_4 (Cơ sở 2)</t>
         </is>
       </c>
       <c r="F61" t="n">
@@ -5359,7 +5359,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>20260601_2 (Cơ sở 2), 20260602_2 (Cơ sở 2), 20260602_3 (Cơ sở 2), 20260602_4 (Cơ sở 2), 20260612_4 (Cơ sở 2)</t>
+          <t>20260604_3 (Cơ sở 2), 20260605_2 (Cơ sở 1), 20260605_3 (Cơ sở 1), 20260605_4 (Cơ sở 1), 20260608_1 (Cơ sở 2)</t>
         </is>
       </c>
       <c r="F62" t="n">
@@ -5388,7 +5388,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>20260519_5 (Cơ sở 1), 20260528_1 (Cơ sở 1), 20260528_4 (Cơ sở 1), 20260609_2 (Cơ sở 1), 20260610_1 (Cơ sở 1), 20260611_1 (Cơ sở 1)</t>
+          <t>20260528_1 (Cơ sở 1), 20260605_2 (Cơ sở 1), 20260605_3 (Cơ sở 1), 20260610_3 (Cơ sở 1), 20260610_1 (Cơ sở 1), 20260610_2 (Cơ sở 1)</t>
         </is>
       </c>
       <c r="F63" t="n">
@@ -5413,11 +5413,11 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>20260521_5 (Cơ sở 1), 20260528_1 (Cơ sở 1), 20260530_2 (Cơ sở 1), 20260605_4 (Cơ sở 1), 20260612_4 (Cơ sở 1), 20260611_1 (Cơ sở 1)</t>
+          <t>20260530_2 (Cơ sở 1), 20260608_3 (Cơ sở 1), 20260608_4 (Cơ sở 1), 20260611_3 (Cơ sở 1), 20260611_1 (Cơ sở 1)</t>
         </is>
       </c>
       <c r="F64" t="n">
@@ -5442,11 +5442,11 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>20260526_5 (Cơ sở 1), 20260529_1 (Cơ sở 1), 20260605_3 (Cơ sở 1), 20260605_4 (Cơ sở 1), 20260612_3 (Cơ sở 1), 20260613_1 (Cơ sở 1)</t>
+          <t>20260521_5 (Cơ sở 1), 20260528_1 (Cơ sở 1), 20260528_2 (Cơ sở 1), 20260528_3 (Cơ sở 1), 20260528_4 (Cơ sở 1)</t>
         </is>
       </c>
       <c r="F65" t="n">
@@ -5475,7 +5475,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>20260528_3 (Cơ sở 2), 20260602_1 (Cơ sở 2), 20260603_1 (Cơ sở 2), 20260603_3 (Cơ sở 2), 20260608_1 (Cơ sở 2)</t>
+          <t>20260601_5 (Cơ sở 1), 20260602_1 (Cơ sở 2), 20260604_2 (Cơ sở 2), 20260605_4 (Cơ sở 1), 20260608_1 (Cơ sở 2)</t>
         </is>
       </c>
       <c r="F66" t="n">
@@ -5504,7 +5504,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>20260602_1 (Cơ sở 2), 20260603_3 (Cơ sở 2), 20260609_2 (Cơ sở 2), 20260609_3 (Cơ sở 2), 20260608_2 (Cơ sở 2)</t>
+          <t>20260528_3 (Cơ sở 2), 20260609_2 (Cơ sở 2), 20260608_1 (Cơ sở 2), 20260608_3 (Cơ sở 2), 20260608_4 (Cơ sở 2)</t>
         </is>
       </c>
       <c r="F67" t="n">
@@ -5533,7 +5533,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>20260604_2 (Cơ sở 1), 20260605_4 (Cơ sở 1), 20260609_2 (Cơ sở 2), 20260611_3 (Cơ sở 2), 20260608_4 (Cơ sở 2)</t>
+          <t>20260531_3 (Cơ sở 1), 20260601_1 (Cơ sở 2), 20260601_2 (Cơ sở 2), 20260602_5 (Cơ sở 1), 20260603_1 (Cơ sở 2)</t>
         </is>
       </c>
       <c r="F68" t="n">
@@ -5562,7 +5562,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>20260525_2 (Cơ sở 2), 20260603_1 (Cơ sở 2), 20260608_3 (Cơ sở 2), 20260608_4 (Cơ sở 2), 20260610_1 (Cơ sở 2)</t>
+          <t>20260525_2 (Cơ sở 2), 20260601_5 (Cơ sở 1), 20260602_1 (Cơ sở 2), 20260605_4 (Cơ sở 1), 20260608_1 (Cơ sở 2)</t>
         </is>
       </c>
       <c r="F69" t="n">
@@ -5591,7 +5591,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>20260523_3 (Cơ sở 1), 20260527_4 (Cơ sở 1), 20260529_2 (Cơ sở 1), 20260530_2 (Cơ sở 1), 20260530_3 (Cơ sở 1)</t>
+          <t>20260518_5 (Cơ sở 1), 20260519_5 (Cơ sở 1), 20260521_5 (Cơ sở 1), 20260529_2 (Cơ sở 1), 20260530_3 (Cơ sở 1)</t>
         </is>
       </c>
       <c r="F70" t="n">
@@ -5620,7 +5620,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>20260518_5 (Cơ sở 1), 20260519_5 (Cơ sở 1), 20260521_5 (Cơ sở 1), 20260529_3 (Cơ sở 1), 20260605_2 (Cơ sở 1)</t>
+          <t>20260527_5 (Cơ sở 1), 20260528_1 (Cơ sở 1), 20260530_2 (Cơ sở 1), 20260530_3 (Cơ sở 1), 20260531_2 (Cơ sở 1)</t>
         </is>
       </c>
       <c r="F71" t="n">
@@ -5649,7 +5649,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>20260525_2 (Cơ sở 2), 20260601_2 (Cơ sở 2), 20260601_3 (Cơ sở 2), 20260609_3 (Cơ sở 2), 20260613_3 (Cơ sở 2)</t>
+          <t>20260603_2 (Cơ sở 2), 20260613_2 (Cơ sở 2), 20260613_3 (Cơ sở 2), 20260612_3 (Cơ sở 2), 20260612_4 (Cơ sở 2)</t>
         </is>
       </c>
       <c r="F72" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>20260518_5 (Cơ sở 1), 20260601_5 (Cơ sở 1), 20260608_3 (Cơ sở 1), 20260612_3 (Cơ sở 1), 20260613_3 (Cơ sở 1)</t>
+          <t>20260608_2 (Cơ sở 1), 20260608_3 (Cơ sở 1), 20260608_4 (Cơ sở 1), 20260609_2 (Cơ sở 1), 20260613_3 (Cơ sở 1)</t>
         </is>
       </c>
       <c r="F73" t="n">
@@ -5707,7 +5707,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>20260523_3 (Cơ sở 1), 20260528_1 (Cơ sở 1), 20260531_3 (Cơ sở 1), 20260612_3 (Cơ sở 1), 20260610_1 (Cơ sở 1)</t>
+          <t>20260521_5 (Cơ sở 1), 20260522_5 (Cơ sở 1), 20260523_3 (Cơ sở 1), 20260525_2 (Cơ sở 2), 20260525_5 (Cơ sở 1)</t>
         </is>
       </c>
       <c r="F74" t="n">
@@ -5791,7 +5791,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8">
@@ -5801,7 +5801,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">

--- a/outputs/lich_truc_final.xlsx
+++ b/outputs/lich_truc_final.xlsx
@@ -534,7 +534,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>CB028, CB045, CB052, CB056, CB069</t>
+          <t>CB010, CB023, CB042, CB063, CB073</t>
         </is>
       </c>
     </row>
@@ -572,7 +572,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>CB028, CB045, CB052, CB056, CB069</t>
+          <t>CB010, CB020, CB035, CB063, CB064</t>
         </is>
       </c>
     </row>
@@ -610,7 +610,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>CB020, CB028, CB045, CB052, CB054, CB056, CB064, CB069, CB073</t>
+          <t>CB010, CB015, CB020, CB023, CB026, CB042, CB043, CB054, CB062</t>
         </is>
       </c>
     </row>
@@ -648,7 +648,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>CB020, CB054, CB073</t>
+          <t>CB031, CB037, CB062</t>
         </is>
       </c>
     </row>
@@ -686,7 +686,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>CB020, CB022, CB054, CB073</t>
+          <t>CB022, CB028, CB059, CB073</t>
         </is>
       </c>
     </row>
@@ -724,7 +724,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>CB006, CB013, CB020, CB022, CB035, CB054, CB058, CB068, CB073</t>
+          <t>CB003, CB007, CB012, CB013, CB036, CB040, CB046, CB055, CB065</t>
         </is>
       </c>
     </row>
@@ -762,7 +762,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>CB020, CB022, CB032, CB050, CB054, CB073</t>
+          <t>CB002, CB011, CB028, CB039, CB043, CB047</t>
         </is>
       </c>
     </row>
@@ -800,7 +800,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>CB022, CB032, CB050</t>
+          <t>CB031, CB039, CB049</t>
         </is>
       </c>
     </row>
@@ -838,7 +838,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>CB013, CB022, CB032, CB050</t>
+          <t>CB007, CB009, CB018, CB046</t>
         </is>
       </c>
     </row>
@@ -876,7 +876,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>CB035</t>
+          <t>CB011</t>
         </is>
       </c>
     </row>
@@ -914,7 +914,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>CB070</t>
+          <t>CB028</t>
         </is>
       </c>
     </row>
@@ -952,7 +952,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>CB031, CB049, CB062, CB064, CB070</t>
+          <t>CB033, CB034, CB056, CB067, CB069</t>
         </is>
       </c>
     </row>
@@ -990,7 +990,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>CB031, CB049, CB064</t>
+          <t>CB016, CB044, CB064</t>
         </is>
       </c>
     </row>
@@ -1028,7 +1028,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>CB006, CB007, CB013, CB038, CB041, CB046, CB055, CB057, CB066</t>
+          <t>CB005, CB006, CB024, CB025, CB027, CB058, CB060, CB065, CB068</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>CB064</t>
+          <t>CB019</t>
         </is>
       </c>
     </row>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>CB010, CB014, CB031, CB034, CB037, CB049, CB064</t>
+          <t>CB020, CB033, CB037, CB043, CB056, CB063, CB067</t>
         </is>
       </c>
     </row>
@@ -1142,7 +1142,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>CB014, CB033</t>
+          <t>CB016, CB064</t>
         </is>
       </c>
     </row>
@@ -1180,7 +1180,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>CB006, CB007, CB021, CB029, CB038, CB053, CB055</t>
+          <t>CB003, CB008, CB030, CB038, CB040, CB051, CB065</t>
         </is>
       </c>
     </row>
@@ -1218,7 +1218,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>CB011, CB014, CB033, CB037, CB042, CB043</t>
+          <t>CB004, CB015, CB016, CB039, CB062, CB072</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1256,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>CB011, CB014, CB033, CB037, CB042, CB043, CB069</t>
+          <t>CB002, CB045, CB047, CB049, CB052, CB056, CB067</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>CB010, CB011, CB031, CB042, CB043</t>
+          <t>CB023, CB044, CB050, CB054, CB069</t>
         </is>
       </c>
     </row>
@@ -1332,7 +1332,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>CB043</t>
+          <t>CB002</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>CB042, CB043, CB045, CB047, CB063, CB070</t>
+          <t>CB002, CB011, CB031, CB045, CB059, CB069</t>
         </is>
       </c>
     </row>
@@ -1408,7 +1408,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>CB010, CB023, CB031, CB042, CB043, CB045, CB047, CB069, CB070</t>
+          <t>CB015, CB016, CB019, CB026, CB028, CB034, CB043, CB044, CB047</t>
         </is>
       </c>
     </row>
@@ -1446,7 +1446,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>CB023, CB070</t>
+          <t>CB019, CB026</t>
         </is>
       </c>
     </row>
@@ -1484,7 +1484,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>CB067</t>
+          <t>CB039</t>
         </is>
       </c>
     </row>
@@ -1522,7 +1522,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>CB001, CB018, CB024, CB036, CB057, CB067</t>
+          <t>CB001, CB005, CB009, CB027, CB032, CB051</t>
         </is>
       </c>
     </row>
@@ -1560,7 +1560,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>CB001, CB018, CB024, CB036, CB057, CB067</t>
+          <t>CB008, CB017, CB030, CB048, CB058, CB060</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>CB001, CB018, CB024, CB036, CB057</t>
+          <t>CB036, CB040, CB041, CB057, CB068</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1636,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>CB001, CB013, CB018, CB024, CB036, CB040, CB057</t>
+          <t>CB001, CB005, CB009, CB027, CB032, CB051, CB066</t>
         </is>
       </c>
     </row>
@@ -1674,7 +1674,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>CB012, CB017, CB035, CB045, CB051, CB059, CB060, CB065, CB068</t>
+          <t>CB014, CB015, CB019, CB023, CB045, CB069, CB070, CB072, CB073</t>
         </is>
       </c>
     </row>
@@ -1712,7 +1712,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>CB012, CB017, CB035, CB051, CB060, CB065, CB068</t>
+          <t>CB009, CB012, CB025, CB029, CB048, CB055, CB058</t>
         </is>
       </c>
     </row>
@@ -1750,7 +1750,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>CB012, CB051, CB060</t>
+          <t>CB021, CB040, CB053</t>
         </is>
       </c>
     </row>
@@ -1788,7 +1788,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>CB012, CB051, CB060</t>
+          <t>CB013, CB017, CB046</t>
         </is>
       </c>
     </row>
@@ -1826,7 +1826,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>CB006, CB012, CB024, CB025, CB041, CB051, CB060</t>
+          <t>CB003, CB012, CB048, CB055, CB058, CB060, CB065</t>
         </is>
       </c>
     </row>
@@ -1864,7 +1864,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>CB004, CB027, CB067</t>
+          <t>CB014, CB063, CB072</t>
         </is>
       </c>
     </row>
@@ -1902,7 +1902,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>CB003, CB004, CB007, CB009, CB017, CB021, CB025, CB027, CB067</t>
+          <t>CB007, CB021, CB024, CB029, CB040, CB046, CB051, CB053, CB071</t>
         </is>
       </c>
     </row>
@@ -1940,7 +1940,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>CB007, CB009, CB021, CB025, CB071</t>
+          <t>CB001, CB005, CB036, CB041, CB060</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>CB003, CB007, CB009, CB021, CB025, CB038, CB040</t>
+          <t>CB003, CB008, CB017, CB030, CB057, CB061, CB066</t>
         </is>
       </c>
     </row>
@@ -2016,7 +2016,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>CB003</t>
+          <t>CB007</t>
         </is>
       </c>
     </row>
@@ -2054,7 +2054,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>CB003</t>
+          <t>CB057</t>
         </is>
       </c>
     </row>
@@ -2092,7 +2092,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>CB003, CB004, CB009, CB025, CB038, CB058, CB065</t>
+          <t>CB012, CB024, CB027, CB036, CB061, CB066, CB071</t>
         </is>
       </c>
     </row>
@@ -2130,7 +2130,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>CB002, CB016, CB028, CB034</t>
+          <t>CB014, CB054, CB070, CB073</t>
         </is>
       </c>
     </row>
@@ -2168,7 +2168,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>CB061</t>
+          <t>CB041</t>
         </is>
       </c>
     </row>
@@ -2206,7 +2206,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>CB010, CB011, CB015, CB016, CB034, CB047, CB061, CB062</t>
+          <t>CB004, CB010, CB011, CB019, CB022, CB045, CB047, CB062</t>
         </is>
       </c>
     </row>
@@ -2244,7 +2244,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>CB010, CB011, CB015, CB016, CB034, CB047, CB061, CB062</t>
+          <t>CB026, CB028, CB039, CB042, CB049, CB050, CB056, CB073</t>
         </is>
       </c>
     </row>
@@ -2282,7 +2282,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>CB004, CB017, CB027, CB050, CB061, CB065, CB068</t>
+          <t>CB002, CB020, CB033, CB043, CB052, CB054, CB064</t>
         </is>
       </c>
     </row>
@@ -2320,7 +2320,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>CB023, CB037, CB072</t>
+          <t>CB022, CB047, CB054</t>
         </is>
       </c>
     </row>
@@ -2358,7 +2358,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>CB002, CB011, CB015, CB023, CB037, CB039, CB049, CB063, CB072</t>
+          <t>CB004, CB015, CB016, CB020, CB034, CB050, CB067, CB069, CB072</t>
         </is>
       </c>
     </row>
@@ -2396,7 +2396,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>CB015, CB023, CB039, CB049, CB063, CB072</t>
+          <t>CB023, CB026, CB059, CB062, CB063, CB070</t>
         </is>
       </c>
     </row>
@@ -2434,7 +2434,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>CB005, CB008, CB018, CB029, CB046, CB048, CB053, CB066</t>
+          <t>CB008, CB009, CB018, CB029, CB038, CB061, CB068, CB071</t>
         </is>
       </c>
     </row>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>CB015, CB023, CB072</t>
+          <t>CB022, CB033, CB037</t>
         </is>
       </c>
     </row>
@@ -2510,7 +2510,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>CB005, CB030, CB046, CB048</t>
+          <t>CB036, CB041, CB048, CB055</t>
         </is>
       </c>
     </row>
@@ -2548,7 +2548,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>CB001</t>
+          <t>CB024</t>
         </is>
       </c>
     </row>
@@ -2586,7 +2586,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>CB015, CB031, CB033, CB044, CB062</t>
+          <t>CB022, CB031, CB033, CB052, CB072</t>
         </is>
       </c>
     </row>
@@ -2624,7 +2624,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>CB013, CB027, CB036, CB040, CB041</t>
+          <t>CB001, CB007, CB012, CB053, CB061</t>
         </is>
       </c>
     </row>
@@ -2662,7 +2662,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>CB002, CB044, CB059, CB063</t>
+          <t>CB011, CB016, CB045, CB070</t>
         </is>
       </c>
     </row>
@@ -2700,7 +2700,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>CB002, CB059</t>
+          <t>CB004, CB042</t>
         </is>
       </c>
     </row>
@@ -2738,7 +2738,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>CB002, CB016, CB019, CB026, CB034, CB039, CB056, CB059</t>
+          <t>CB034, CB044, CB047, CB052, CB056, CB059, CB063, CB064</t>
         </is>
       </c>
     </row>
@@ -2776,7 +2776,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>CB016, CB019, CB026, CB056</t>
+          <t>CB002, CB011, CB037, CB039</t>
         </is>
       </c>
     </row>
@@ -2814,7 +2814,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>CB019, CB026, CB039</t>
+          <t>CB004, CB023, CB042</t>
         </is>
       </c>
     </row>
@@ -2852,7 +2852,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>CB019, CB026, CB032, CB039</t>
+          <t>CB031, CB034, CB043, CB050</t>
         </is>
       </c>
     </row>
@@ -2890,7 +2890,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>CB008, CB009, CB040, CB041, CB053, CB055, CB058, CB071</t>
+          <t>CB005, CB006, CB008, CB017, CB018, CB024, CB041, CB046</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>CB019</t>
+          <t>CB045</t>
         </is>
       </c>
     </row>
@@ -2966,7 +2966,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>CB008, CB009, CB029, CB040, CB041, CB053, CB055, CB058, CB071</t>
+          <t>CB025, CB029, CB032, CB038, CB053, CB060, CB061, CB065, CB066</t>
         </is>
       </c>
     </row>
@@ -3004,7 +3004,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>CB019, CB026, CB028, CB037, CB047, CB072</t>
+          <t>CB014, CB015, CB044, CB052, CB062, CB069</t>
         </is>
       </c>
     </row>
@@ -3042,7 +3042,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>CB055</t>
+          <t>CB001</t>
         </is>
       </c>
     </row>
@@ -3080,7 +3080,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>CB047</t>
+          <t>CB034</t>
         </is>
       </c>
     </row>
@@ -3118,7 +3118,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>CB004, CB017, CB027, CB050, CB061, CB065, CB066, CB068</t>
+          <t>CB018, CB021, CB030, CB038, CB046, CB055, CB068, CB071</t>
         </is>
       </c>
     </row>
@@ -3156,7 +3156,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>CB008, CB030</t>
+          <t>CB006, CB057</t>
         </is>
       </c>
     </row>
@@ -3194,7 +3194,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>CB008, CB030, CB066</t>
+          <t>CB013, CB025, CB029</t>
         </is>
       </c>
     </row>
@@ -3232,7 +3232,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>CB005, CB008, CB018, CB029, CB030, CB046, CB048, CB053, CB066</t>
+          <t>CB007, CB018, CB021, CB030, CB032, CB038, CB053, CB068, CB071</t>
         </is>
       </c>
     </row>
@@ -3270,7 +3270,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>CB005, CB006, CB029, CB046, CB048</t>
+          <t>CB006, CB013, CB017, CB057, CB066</t>
         </is>
       </c>
     </row>
@@ -3308,7 +3308,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>CB005, CB006, CB007, CB029, CB046, CB048</t>
+          <t>CB003, CB018, CB021, CB027, CB032, CB051</t>
         </is>
       </c>
     </row>
@@ -3346,7 +3346,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>CB014, CB044, CB062</t>
+          <t>CB014, CB049, CB059</t>
         </is>
       </c>
     </row>
@@ -3384,7 +3384,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>CB044, CB062</t>
+          <t>CB010, CB028</t>
         </is>
       </c>
     </row>
@@ -3422,7 +3422,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>CB044, CB052</t>
+          <t>CB049, CB070</t>
         </is>
       </c>
     </row>
@@ -3460,7 +3460,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>CB002, CB016, CB028, CB033, CB034, CB044, CB052, CB059, CB063</t>
+          <t>CB019, CB026, CB031, CB037, CB042, CB044, CB050, CB064, CB067</t>
         </is>
       </c>
     </row>
@@ -3498,7 +3498,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>CB071</t>
+          <t>CB009</t>
         </is>
       </c>
     </row>
@@ -3536,7 +3536,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>CB021, CB030, CB032, CB038, CB057, CB058, CB071</t>
+          <t>CB001, CB006, CB013, CB025, CB040, CB048, CB058</t>
         </is>
       </c>
     </row>
@@ -3615,11 +3615,11 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>20260601_1 (Cơ sở 2), 20260601_2 (Cơ sở 2), 20260601_3 (Cơ sở 2), 20260601_4 (Cơ sở 2), 20260610_3 (Cơ sở 2)</t>
+          <t>20260601_1 (Cơ sở 2), 20260601_4 (Cơ sở 2), 20260603_2 (Cơ sở 2), 20260611_3 (Cơ sở 2), 20260613_4 (Cơ sở 2), 20260612_4 (Cơ sở 2)</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -3648,7 +3648,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>20260604_2 (Cơ sở 1), 20260608_3 (Cơ sở 1), 20260611_3 (Cơ sở 1), 20260612_1 (Cơ sở 1), 20260612_2 (Cơ sở 1), 20260611_1 (Cơ sở 1)</t>
+          <t>20260525_5 (Cơ sở 1), 20260529_2 (Cơ sở 1), 20260529_5 (Cơ sở 1), 20260530_2 (Cơ sở 1), 20260605_4 (Cơ sở 1), 20260612_3 (Cơ sở 1)</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -3677,7 +3677,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>20260603_1 (Cơ sở 2), 20260603_3 (Cơ sở 2), 20260603_4 (Cơ sở 2), 20260604_1 (Cơ sở 2), 20260604_2 (Cơ sở 2)</t>
+          <t>20260525_2 (Cơ sở 2), 20260529_1 (Cơ sở 2), 20260602_4 (Cơ sở 2), 20260603_3 (Cơ sở 2), 20260610_1 (Cơ sở 2)</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>20260602_5 (Cơ sở 1), 20260603_1 (Cơ sở 2), 20260604_2 (Cơ sở 2), 20260605_4 (Cơ sở 1), 20260608_1 (Cơ sở 2)</t>
+          <t>20260529_1 (Cơ sở 1), 20260605_2 (Cơ sở 1), 20260608_3 (Cơ sở 1), 20260612_1 (Cơ sở 1), 20260612_4 (Cơ sở 1)</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -3735,7 +3735,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>20260609_2 (Cơ sở 2), 20260609_3 (Cơ sở 2), 20260608_4 (Cơ sở 2), 20260609_4 (Cơ sở 2), 20260610_1 (Cơ sở 2)</t>
+          <t>20260528_3 (Cơ sở 2), 20260601_1 (Cơ sở 2), 20260601_4 (Cơ sở 2), 20260603_2 (Cơ sở 2), 20260613_2 (Cơ sở 2)</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -3760,11 +3760,11 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>20260525_2 (Cơ sở 2), 20260528_3 (Cơ sở 2), 20260529_1 (Cơ sở 2), 20260602_4 (Cơ sở 2), 20260609_4 (Cơ sở 2), 20260610_1 (Cơ sở 2)</t>
+          <t>20260528_3 (Cơ sở 2), 20260613_2 (Cơ sở 2), 20260608_2 (Cơ sở 2), 20260609_4 (Cơ sở 2), 20260612_4 (Cơ sở 2)</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -3793,7 +3793,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>20260528_3 (Cơ sở 2), 20260529_1 (Cơ sở 2), 20260603_1 (Cơ sở 2), 20260603_2 (Cơ sở 2), 20260603_3 (Cơ sở 2), 20260610_1 (Cơ sở 2)</t>
+          <t>20260525_2 (Cơ sở 2), 20260527_2 (Cơ sở 2), 20260603_1 (Cơ sở 2), 20260603_4 (Cơ sở 2), 20260611_3 (Cơ sở 2), 20260608_4 (Cơ sở 2)</t>
         </is>
       </c>
       <c r="F8" t="n">
@@ -3818,11 +3818,11 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>20260609_2 (Cơ sở 2), 20260613_2 (Cơ sở 2), 20260613_3 (Cơ sở 2), 20260608_2 (Cơ sở 2), 20260608_3 (Cơ sở 2), 20260608_4 (Cơ sở 2)</t>
+          <t>20260529_1 (Cơ sở 2), 20260601_2 (Cơ sở 2), 20260603_3 (Cơ sở 2), 20260609_2 (Cơ sở 2), 20260613_2 (Cơ sở 2)</t>
         </is>
       </c>
       <c r="F9" t="n">
@@ -3851,7 +3851,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>20260603_1 (Cơ sở 2), 20260603_2 (Cơ sở 2), 20260603_3 (Cơ sở 2), 20260604_2 (Cơ sở 2), 20260613_2 (Cơ sở 2), 20260613_3 (Cơ sở 2)</t>
+          <t>20260527_2 (Cơ sở 2), 20260601_1 (Cơ sở 2), 20260601_4 (Cơ sở 2), 20260602_1 (Cơ sở 2), 20260609_2 (Cơ sở 2), 20260612_3 (Cơ sở 2)</t>
         </is>
       </c>
       <c r="F10" t="n">
@@ -3880,7 +3880,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>20260528_4 (Cơ sở 1), 20260529_3 (Cơ sở 1), 20260530_3 (Cơ sở 1), 20260605_2 (Cơ sở 1), 20260605_3 (Cơ sở 1)</t>
+          <t>20260518_5 (Cơ sở 1), 20260519_5 (Cơ sở 1), 20260521_5 (Cơ sở 1), 20260605_2 (Cơ sở 1), 20260610_2 (Cơ sở 1)</t>
         </is>
       </c>
       <c r="F11" t="n">
@@ -3909,7 +3909,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>20260529_1 (Cơ sở 1), 20260529_2 (Cơ sở 1), 20260529_3 (Cơ sở 1), 20260605_2 (Cơ sở 1), 20260605_3 (Cơ sở 1), 20260608_3 (Cơ sở 1)</t>
+          <t>20260525_5 (Cơ sở 1), 20260527_4 (Cơ sở 1), 20260530_2 (Cơ sở 1), 20260605_2 (Cơ sở 1), 20260611_3 (Cơ sở 1), 20260612_3 (Cơ sở 1)</t>
         </is>
       </c>
       <c r="F12" t="n">
@@ -3938,7 +3938,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>20260601_5 (Cơ sở 1), 20260602_1 (Cơ sở 2), 20260602_2 (Cơ sở 2), 20260602_3 (Cơ sở 2), 20260602_4 (Cơ sở 2)</t>
+          <t>20260525_2 (Cơ sở 2), 20260602_1 (Cơ sở 2), 20260602_4 (Cơ sở 2), 20260604_2 (Cơ sở 2), 20260611_3 (Cơ sở 2)</t>
         </is>
       </c>
       <c r="F13" t="n">
@@ -3967,7 +3967,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>20260525_2 (Cơ sở 2), 20260527_2 (Cơ sở 2), 20260528_3 (Cơ sở 2), 20260601_4 (Cơ sở 2), 20260611_3 (Cơ sở 2)</t>
+          <t>20260525_2 (Cơ sở 2), 20260602_3 (Cơ sở 2), 20260608_3 (Cơ sở 2), 20260609_4 (Cơ sở 2), 20260612_4 (Cơ sở 2)</t>
         </is>
       </c>
       <c r="F14" t="n">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>20260528_4 (Cơ sở 1), 20260528_5 (Cơ sở 1), 20260529_1 (Cơ sở 1), 20260529_2 (Cơ sở 1), 20260610_1 (Cơ sở 1)</t>
+          <t>20260601_5 (Cơ sở 1), 20260602_5 (Cơ sở 1), 20260604_2 (Cơ sở 1), 20260613_3 (Cơ sở 1), 20260610_1 (Cơ sở 1)</t>
         </is>
       </c>
       <c r="F15" t="n">
@@ -4025,7 +4025,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>20260605_2 (Cơ sở 1), 20260605_3 (Cơ sở 1), 20260608_3 (Cơ sở 1), 20260608_4 (Cơ sở 1), 20260609_2 (Cơ sở 1), 20260610_3 (Cơ sở 1)</t>
+          <t>20260521_5 (Cơ sở 1), 20260529_1 (Cơ sở 1), 20260530_3 (Cơ sở 1), 20260601_5 (Cơ sở 1), 20260608_3 (Cơ sở 1), 20260613_3 (Cơ sở 1)</t>
         </is>
       </c>
       <c r="F16" t="n">
@@ -4054,7 +4054,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>20260604_2 (Cơ sở 1), 20260605_2 (Cơ sở 1), 20260605_3 (Cơ sở 1), 20260612_2 (Cơ sở 1), 20260612_3 (Cơ sở 1), 20260611_1 (Cơ sở 1)</t>
+          <t>20260528_2 (Cơ sở 1), 20260528_5 (Cơ sở 1), 20260529_1 (Cơ sở 1), 20260530_3 (Cơ sở 1), 20260608_3 (Cơ sở 1), 20260611_3 (Cơ sở 1)</t>
         </is>
       </c>
       <c r="F17" t="n">
@@ -4083,7 +4083,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>20260601_5 (Cơ sở 1), 20260602_1 (Cơ sở 2), 20260603_1 (Cơ sở 2), 20260605_4 (Cơ sở 1), 20260608_1 (Cơ sở 2)</t>
+          <t>20260601_2 (Cơ sở 2), 20260602_3 (Cơ sở 2), 20260603_3 (Cơ sở 2), 20260613_2 (Cơ sở 2), 20260609_4 (Cơ sở 2)</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -4112,7 +4112,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>20260601_1 (Cơ sở 2), 20260601_2 (Cơ sở 2), 20260601_3 (Cơ sở 2), 20260601_4 (Cơ sở 2), 20260609_2 (Cơ sở 2), 20260608_4 (Cơ sở 2)</t>
+          <t>20260527_2 (Cơ sở 2), 20260609_2 (Cơ sở 2), 20260613_2 (Cơ sở 2), 20260608_1 (Cơ sở 2), 20260608_4 (Cơ sở 2), 20260610_1 (Cơ sở 2)</t>
         </is>
       </c>
       <c r="F19" t="n">
@@ -4141,7 +4141,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>20260612_2 (Cơ sở 1), 20260612_3 (Cơ sở 1), 20260612_4 (Cơ sở 1), 20260613_1 (Cơ sở 1), 20260613_2 (Cơ sở 1), 20260613_3 (Cơ sở 1)</t>
+          <t>20260528_3 (Cơ sở 1), 20260530_3 (Cơ sở 1), 20260531_2 (Cơ sở 1), 20260601_5 (Cơ sở 1), 20260605_2 (Cơ sở 1), 20260611_1 (Cơ sở 1)</t>
         </is>
       </c>
       <c r="F20" t="n">
@@ -4170,7 +4170,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>20260521_5 (Cơ sở 1), 20260522_5 (Cơ sở 1), 20260523_3 (Cơ sở 1), 20260525_2 (Cơ sở 2), 20260525_5 (Cơ sở 1)</t>
+          <t>20260519_5 (Cơ sở 1), 20260521_5 (Cơ sở 1), 20260528_4 (Cơ sở 1), 20260605_4 (Cơ sở 1), 20260608_3 (Cơ sở 1)</t>
         </is>
       </c>
       <c r="F21" t="n">
@@ -4199,7 +4199,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>20260529_1 (Cơ sở 2), 20260603_1 (Cơ sở 2), 20260603_2 (Cơ sở 2), 20260603_3 (Cơ sở 2), 20260612_4 (Cơ sở 2)</t>
+          <t>20260602_2 (Cơ sở 2), 20260603_1 (Cơ sở 2), 20260608_1 (Cơ sở 2), 20260608_4 (Cơ sở 2), 20260610_1 (Cơ sở 2)</t>
         </is>
       </c>
       <c r="F22" t="n">
@@ -4228,7 +4228,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>20260523_3 (Cơ sở 1), 20260525_2 (Cơ sở 2), 20260525_5 (Cơ sở 1), 20260526_5 (Cơ sở 1), 20260527_2 (Cơ sở 2)</t>
+          <t>20260523_3 (Cơ sở 1), 20260605_2 (Cơ sở 1), 20260608_2 (Cơ sở 1), 20260609_2 (Cơ sở 1), 20260610_3 (Cơ sở 1)</t>
         </is>
       </c>
       <c r="F23" t="n">
@@ -4257,7 +4257,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>20260530_3 (Cơ sở 1), 20260531_2 (Cơ sở 1), 20260608_2 (Cơ sở 1), 20260608_3 (Cơ sở 1), 20260608_4 (Cơ sở 1), 20260609_2 (Cơ sở 1)</t>
+          <t>20260518_5 (Cơ sở 1), 20260521_5 (Cơ sở 1), 20260529_3 (Cơ sở 1), 20260601_5 (Cơ sở 1), 20260608_4 (Cơ sở 1), 20260612_4 (Cơ sở 1)</t>
         </is>
       </c>
       <c r="F24" t="n">
@@ -4286,7 +4286,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>20260601_1 (Cơ sở 2), 20260601_2 (Cơ sở 2), 20260601_3 (Cơ sở 2), 20260601_4 (Cơ sở 2), 20260602_4 (Cơ sở 2)</t>
+          <t>20260528_3 (Cơ sở 2), 20260603_1 (Cơ sở 2), 20260604_2 (Cơ sở 2), 20260610_3 (Cơ sở 2), 20260613_2 (Cơ sở 2)</t>
         </is>
       </c>
       <c r="F25" t="n">
@@ -4315,7 +4315,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>20260602_4 (Cơ sở 2), 20260603_1 (Cơ sở 2), 20260603_2 (Cơ sở 2), 20260603_3 (Cơ sở 2), 20260604_2 (Cơ sở 2)</t>
+          <t>20260528_3 (Cơ sở 2), 20260602_1 (Cơ sở 2), 20260613_3 (Cơ sở 2), 20260608_3 (Cơ sở 2), 20260612_4 (Cơ sở 2)</t>
         </is>
       </c>
       <c r="F26" t="n">
@@ -4340,11 +4340,11 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>20260612_2 (Cơ sở 1), 20260612_3 (Cơ sở 1), 20260612_4 (Cơ sở 1), 20260613_1 (Cơ sở 1), 20260613_3 (Cơ sở 1)</t>
+          <t>20260521_5 (Cơ sở 1), 20260530_3 (Cơ sở 1), 20260531_2 (Cơ sở 1), 20260605_3 (Cơ sở 1), 20260608_4 (Cơ sở 1), 20260611_1 (Cơ sở 1)</t>
         </is>
       </c>
       <c r="F27" t="n">
@@ -4373,7 +4373,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>20260602_5 (Cơ sở 1), 20260603_1 (Cơ sở 2), 20260605_4 (Cơ sở 1), 20260611_3 (Cơ sở 2), 20260608_1 (Cơ sở 2)</t>
+          <t>20260528_3 (Cơ sở 2), 20260601_1 (Cơ sở 2), 20260601_4 (Cơ sở 2), 20260604_2 (Cơ sở 2), 20260610_1 (Cơ sở 2)</t>
         </is>
       </c>
       <c r="F28" t="n">
@@ -4402,7 +4402,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>20260518_5 (Cơ sở 1), 20260519_5 (Cơ sở 1), 20260521_5 (Cơ sở 1), 20260604_2 (Cơ sở 1), 20260613_3 (Cơ sở 1), 20260611_1 (Cơ sở 1)</t>
+          <t>20260523_3 (Cơ sở 1), 20260525_5 (Cơ sở 1), 20260527_5 (Cơ sở 1), 20260530_3 (Cơ sở 1), 20260605_3 (Cơ sở 1), 20260610_2 (Cơ sở 1)</t>
         </is>
       </c>
       <c r="F29" t="n">
@@ -4427,11 +4427,11 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>20260529_1 (Cơ sở 2), 20260609_2 (Cơ sở 2), 20260613_3 (Cơ sở 2), 20260608_4 (Cơ sở 2), 20260609_4 (Cơ sở 2), 20260610_1 (Cơ sở 2)</t>
+          <t>20260602_1 (Cơ sở 2), 20260603_1 (Cơ sở 2), 20260609_2 (Cơ sở 2), 20260613_3 (Cơ sở 2), 20260608_3 (Cơ sở 2)</t>
         </is>
       </c>
       <c r="F30" t="n">
@@ -4460,7 +4460,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>20260609_3 (Cơ sở 2), 20260608_2 (Cơ sở 2), 20260608_3 (Cơ sở 2), 20260608_4 (Cơ sở 2), 20260612_4 (Cơ sở 2)</t>
+          <t>20260529_1 (Cơ sở 2), 20260601_2 (Cơ sở 2), 20260603_3 (Cơ sở 2), 20260608_1 (Cơ sở 2), 20260608_4 (Cơ sở 2)</t>
         </is>
       </c>
       <c r="F31" t="n">
@@ -4489,7 +4489,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>20260528_1 (Cơ sở 1), 20260528_2 (Cơ sở 1), 20260528_4 (Cơ sở 1), 20260529_3 (Cơ sở 1), 20260530_3 (Cơ sở 1), 20260610_3 (Cơ sở 1)</t>
+          <t>20260522_5 (Cơ sở 1), 20260526_5 (Cơ sở 1), 20260530_2 (Cơ sở 1), 20260610_3 (Cơ sở 1), 20260613_1 (Cơ sở 1), 20260611_1 (Cơ sở 1)</t>
         </is>
       </c>
       <c r="F32" t="n">
@@ -4518,7 +4518,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>20260525_5 (Cơ sở 1), 20260526_5 (Cơ sở 1), 20260527_2 (Cơ sở 2), 20260613_1 (Cơ sở 1), 20260612_4 (Cơ sở 2)</t>
+          <t>20260601_1 (Cơ sở 2), 20260601_4 (Cơ sở 2), 20260613_3 (Cơ sở 2), 20260608_4 (Cơ sở 2), 20260610_1 (Cơ sở 2)</t>
         </is>
       </c>
       <c r="F33" t="n">
@@ -4547,7 +4547,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>20260528_5 (Cơ sở 1), 20260529_1 (Cơ sở 1), 20260529_2 (Cơ sở 1), 20260610_3 (Cơ sở 1), 20260611_1 (Cơ sở 1)</t>
+          <t>20260528_1 (Cơ sở 1), 20260528_4 (Cơ sở 1), 20260605_4 (Cơ sở 1), 20260609_2 (Cơ sở 1), 20260610_3 (Cơ sở 1)</t>
         </is>
       </c>
       <c r="F34" t="n">
@@ -4576,7 +4576,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>20260528_4 (Cơ sở 1), 20260604_2 (Cơ sở 1), 20260605_2 (Cơ sở 1), 20260605_3 (Cơ sở 1), 20260612_2 (Cơ sở 1), 20260611_1 (Cơ sở 1)</t>
+          <t>20260528_1 (Cơ sở 1), 20260530_3 (Cơ sở 1), 20260608_3 (Cơ sở 1), 20260612_2 (Cơ sở 1), 20260613_1 (Cơ sở 1), 20260613_4 (Cơ sở 1)</t>
         </is>
       </c>
       <c r="F35" t="n">
@@ -4601,11 +4601,11 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>20260525_2 (Cơ sở 2), 20260527_4 (Cơ sở 1), 20260601_5 (Cơ sở 1), 20260602_1 (Cơ sở 2)</t>
+          <t>20260519_5 (Cơ sở 1)</t>
         </is>
       </c>
       <c r="F36" t="n">
@@ -4634,7 +4634,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>20260601_1 (Cơ sở 2), 20260601_2 (Cơ sở 2), 20260601_3 (Cơ sở 2), 20260601_4 (Cơ sở 2), 20260611_3 (Cơ sở 2)</t>
+          <t>20260525_2 (Cơ sở 2), 20260601_3 (Cơ sở 2), 20260603_2 (Cơ sở 2), 20260604_2 (Cơ sở 2), 20260609_3 (Cơ sở 2)</t>
         </is>
       </c>
       <c r="F37" t="n">
@@ -4659,11 +4659,11 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>20260528_4 (Cơ sở 1), 20260529_1 (Cơ sở 1), 20260529_2 (Cơ sở 1), 20260608_2 (Cơ sở 1), 20260608_3 (Cơ sở 1), 20260613_3 (Cơ sở 1)</t>
+          <t>20260522_5 (Cơ sở 1), 20260528_4 (Cơ sở 1), 20260609_2 (Cơ sở 1), 20260612_3 (Cơ sở 1), 20260611_1 (Cơ sở 1)</t>
         </is>
       </c>
       <c r="F38" t="n">
@@ -4692,7 +4692,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>20260528_3 (Cơ sở 2), 20260529_1 (Cơ sở 2), 20260603_3 (Cơ sở 2), 20260604_2 (Cơ sở 2), 20260612_4 (Cơ sở 2)</t>
+          <t>20260529_1 (Cơ sở 2), 20260609_2 (Cơ sở 2), 20260613_3 (Cơ sở 2), 20260608_1 (Cơ sở 2), 20260608_4 (Cơ sở 2)</t>
         </is>
       </c>
       <c r="F39" t="n">
@@ -4717,11 +4717,11 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>20260608_3 (Cơ sở 1), 20260608_4 (Cơ sở 1), 20260612_2 (Cơ sở 1), 20260612_4 (Cơ sở 1), 20260613_1 (Cơ sở 1)</t>
+          <t>20260525_5 (Cơ sở 1), 20260526_5 (Cơ sở 1), 20260529_1 (Cơ sở 1), 20260531_3 (Cơ sở 1), 20260605_3 (Cơ sở 1), 20260612_3 (Cơ sở 1)</t>
         </is>
       </c>
       <c r="F40" t="n">
@@ -4746,11 +4746,11 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>20260601_4 (Cơ sở 2), 20260603_3 (Cơ sở 2), 20260611_3 (Cơ sở 2), 20260613_2 (Cơ sở 2), 20260613_3 (Cơ sở 2)</t>
+          <t>20260525_2 (Cơ sở 2), 20260529_1 (Cơ sở 2), 20260601_3 (Cơ sở 2), 20260602_2 (Cơ sở 2), 20260603_1 (Cơ sở 2), 20260612_4 (Cơ sở 2)</t>
         </is>
       </c>
       <c r="F41" t="n">
@@ -4779,7 +4779,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>20260528_3 (Cơ sở 2), 20260602_4 (Cơ sở 2), 20260611_3 (Cơ sở 2), 20260613_2 (Cơ sở 2), 20260613_3 (Cơ sở 2)</t>
+          <t>20260601_3 (Cơ sở 2), 20260603_2 (Cơ sở 2), 20260604_3 (Cơ sở 2), 20260609_3 (Cơ sở 2), 20260613_2 (Cơ sở 2)</t>
         </is>
       </c>
       <c r="F42" t="n">
@@ -4804,11 +4804,11 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>20260529_1 (Cơ sở 1), 20260529_2 (Cơ sở 1), 20260529_3 (Cơ sở 1), 20260530_2 (Cơ sở 1), 20260530_3 (Cơ sở 1)</t>
+          <t>20260518_5 (Cơ sở 1), 20260521_5 (Cơ sở 1), 20260605_3 (Cơ sở 1), 20260612_1 (Cơ sở 1), 20260612_4 (Cơ sở 1), 20260611_1 (Cơ sở 1)</t>
         </is>
       </c>
       <c r="F43" t="n">
@@ -4837,7 +4837,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>20260529_1 (Cơ sở 1), 20260529_2 (Cơ sở 1), 20260529_3 (Cơ sở 1), 20260529_5 (Cơ sở 1), 20260530_2 (Cơ sở 1), 20260530_3 (Cơ sở 1)</t>
+          <t>20260521_5 (Cơ sở 1), 20260525_5 (Cơ sở 1), 20260528_4 (Cơ sở 1), 20260530_3 (Cơ sở 1), 20260605_4 (Cơ sở 1), 20260613_1 (Cơ sở 1)</t>
         </is>
       </c>
       <c r="F44" t="n">
@@ -4866,7 +4866,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>20260610_3 (Cơ sở 1), 20260611_3 (Cơ sở 1), 20260610_1 (Cơ sở 1), 20260610_2 (Cơ sở 1), 20260610_4 (Cơ sở 1), 20260611_1 (Cơ sở 1)</t>
+          <t>20260528_2 (Cơ sở 1), 20260529_3 (Cơ sở 1), 20260530_3 (Cơ sở 1), 20260612_2 (Cơ sở 1), 20260613_3 (Cơ sở 1), 20260611_1 (Cơ sở 1)</t>
         </is>
       </c>
       <c r="F45" t="n">
@@ -4895,7 +4895,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>20260518_5 (Cơ sở 1), 20260519_5 (Cơ sở 1), 20260521_5 (Cơ sở 1), 20260530_2 (Cơ sở 1), 20260530_3 (Cơ sở 1), 20260601_5 (Cơ sở 1)</t>
+          <t>20260529_2 (Cơ sở 1), 20260530_2 (Cơ sở 1), 20260601_5 (Cơ sở 1), 20260605_2 (Cơ sở 1), 20260611_3 (Cơ sở 1), 20260613_2 (Cơ sở 1)</t>
         </is>
       </c>
       <c r="F46" t="n">
@@ -4924,7 +4924,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>20260528_3 (Cơ sở 2), 20260609_2 (Cơ sở 2), 20260609_3 (Cơ sở 2), 20260608_4 (Cơ sở 2), 20260609_4 (Cơ sở 2), 20260610_1 (Cơ sở 2)</t>
+          <t>20260525_2 (Cơ sở 2), 20260527_2 (Cơ sở 2), 20260602_3 (Cơ sở 2), 20260603_1 (Cơ sở 2), 20260613_2 (Cơ sở 2), 20260608_1 (Cơ sở 2)</t>
         </is>
       </c>
       <c r="F47" t="n">
@@ -4953,7 +4953,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>20260530_2 (Cơ sở 1), 20260530_3 (Cơ sở 1), 20260605_2 (Cơ sở 1), 20260605_3 (Cơ sở 1), 20260613_3 (Cơ sở 1), 20260613_4 (Cơ sở 1)</t>
+          <t>20260525_5 (Cơ sở 1), 20260529_2 (Cơ sở 1), 20260530_3 (Cơ sở 1), 20260605_2 (Cơ sở 1), 20260608_2 (Cơ sở 1), 20260612_2 (Cơ sở 1)</t>
         </is>
       </c>
       <c r="F48" t="n">
@@ -4982,7 +4982,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>20260609_2 (Cơ sở 2), 20260609_3 (Cơ sở 2), 20260608_4 (Cơ sở 2), 20260609_4 (Cơ sở 2), 20260610_1 (Cơ sở 2)</t>
+          <t>20260601_2 (Cơ sở 2), 20260602_1 (Cơ sở 2), 20260602_4 (Cơ sở 2), 20260609_3 (Cơ sở 2), 20260612_4 (Cơ sở 2)</t>
         </is>
       </c>
       <c r="F49" t="n">
@@ -5011,7 +5011,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>20260528_1 (Cơ sở 1), 20260528_2 (Cơ sở 1), 20260528_4 (Cơ sở 1), 20260608_3 (Cơ sở 1), 20260608_4 (Cơ sở 1)</t>
+          <t>20260526_5 (Cơ sở 1), 20260529_2 (Cơ sở 1), 20260605_3 (Cơ sở 1), 20260610_1 (Cơ sở 1), 20260610_4 (Cơ sở 1)</t>
         </is>
       </c>
       <c r="F50" t="n">
@@ -5040,7 +5040,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>20260525_5 (Cơ sở 1), 20260526_5 (Cơ sở 1), 20260527_2 (Cơ sở 2), 20260605_4 (Cơ sở 1), 20260608_1 (Cơ sở 2)</t>
+          <t>20260529_3 (Cơ sở 1), 20260605_3 (Cơ sở 1), 20260608_3 (Cơ sở 1), 20260613_1 (Cơ sở 1), 20260611_1 (Cơ sở 1)</t>
         </is>
       </c>
       <c r="F51" t="n">
@@ -5069,7 +5069,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>20260601_5 (Cơ sở 1), 20260602_1 (Cơ sở 2), 20260602_2 (Cơ sở 2), 20260602_3 (Cơ sở 2), 20260602_4 (Cơ sở 2)</t>
+          <t>20260529_1 (Cơ sở 2), 20260601_1 (Cơ sở 2), 20260601_4 (Cơ sở 2), 20260603_1 (Cơ sở 2), 20260610_1 (Cơ sở 2)</t>
         </is>
       </c>
       <c r="F52" t="n">
@@ -5098,7 +5098,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>20260518_5 (Cơ sở 1), 20260519_5 (Cơ sở 1), 20260521_5 (Cơ sở 1), 20260610_4 (Cơ sở 1), 20260611_1 (Cơ sở 1)</t>
+          <t>20260529_2 (Cơ sở 1), 20260605_4 (Cơ sở 1), 20260610_3 (Cơ sở 1), 20260612_2 (Cơ sở 1), 20260613_3 (Cơ sở 1)</t>
         </is>
       </c>
       <c r="F53" t="n">
@@ -5127,7 +5127,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>20260529_1 (Cơ sở 2), 20260609_2 (Cơ sở 2), 20260613_2 (Cơ sở 2), 20260613_3 (Cơ sở 2), 20260608_4 (Cơ sở 2)</t>
+          <t>20260602_2 (Cơ sở 2), 20260603_1 (Cơ sở 2), 20260611_3 (Cơ sở 2), 20260613_3 (Cơ sở 2), 20260608_4 (Cơ sở 2)</t>
         </is>
       </c>
       <c r="F54" t="n">
@@ -5156,7 +5156,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>20260521_5 (Cơ sở 1), 20260522_5 (Cơ sở 1), 20260523_3 (Cơ sở 1), 20260525_2 (Cơ sở 2), 20260525_5 (Cơ sở 1)</t>
+          <t>20260521_5 (Cơ sở 1), 20260529_3 (Cơ sở 1), 20260604_2 (Cơ sở 1), 20260605_4 (Cơ sở 1), 20260608_2 (Cơ sở 1)</t>
         </is>
       </c>
       <c r="F55" t="n">
@@ -5185,7 +5185,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>20260528_3 (Cơ sở 2), 20260529_1 (Cơ sở 2), 20260613_2 (Cơ sở 2), 20260613_3 (Cơ sở 2), 20260613_4 (Cơ sở 2)</t>
+          <t>20260525_2 (Cơ sở 2), 20260602_1 (Cơ sở 2), 20260602_4 (Cơ sở 2), 20260609_3 (Cơ sở 2), 20260608_1 (Cơ sở 2)</t>
         </is>
       </c>
       <c r="F56" t="n">
@@ -5214,7 +5214,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>20260518_5 (Cơ sở 1), 20260519_5 (Cơ sở 1), 20260521_5 (Cơ sở 1), 20260612_2 (Cơ sở 1), 20260612_3 (Cơ sở 1)</t>
+          <t>20260528_1 (Cơ sở 1), 20260528_4 (Cơ sở 1), 20260529_2 (Cơ sở 1), 20260605_3 (Cơ sở 1), 20260612_2 (Cơ sở 1)</t>
         </is>
       </c>
       <c r="F57" t="n">
@@ -5239,11 +5239,11 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>20260528_3 (Cơ sở 2), 20260601_1 (Cơ sở 2), 20260601_2 (Cơ sở 2), 20260601_3 (Cơ sở 2), 20260601_4 (Cơ sở 2), 20260612_4 (Cơ sở 2)</t>
+          <t>20260601_3 (Cơ sở 2), 20260603_3 (Cơ sở 2), 20260604_1 (Cơ sở 2), 20260608_2 (Cơ sở 2), 20260609_4 (Cơ sở 2)</t>
         </is>
       </c>
       <c r="F58" t="n">
@@ -5272,7 +5272,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>20260525_2 (Cơ sở 2), 20260604_2 (Cơ sở 2), 20260613_2 (Cơ sở 2), 20260613_3 (Cơ sở 2), 20260612_4 (Cơ sở 2)</t>
+          <t>20260528_3 (Cơ sở 2), 20260601_2 (Cơ sở 2), 20260602_1 (Cơ sở 2), 20260602_4 (Cơ sở 2), 20260612_4 (Cơ sở 2)</t>
         </is>
       </c>
       <c r="F59" t="n">
@@ -5301,7 +5301,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>20260601_5 (Cơ sở 1), 20260611_3 (Cơ sở 1), 20260612_1 (Cơ sở 1), 20260612_2 (Cơ sở 1), 20260611_1 (Cơ sở 1)</t>
+          <t>20260523_3 (Cơ sở 1), 20260530_2 (Cơ sở 1), 20260608_4 (Cơ sở 1), 20260612_2 (Cơ sở 1), 20260610_1 (Cơ sở 1)</t>
         </is>
       </c>
       <c r="F60" t="n">
@@ -5330,7 +5330,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>20260601_5 (Cơ sở 1), 20260602_1 (Cơ sở 2), 20260602_2 (Cơ sở 2), 20260602_3 (Cơ sở 2), 20260602_4 (Cơ sở 2)</t>
+          <t>20260528_3 (Cơ sở 2), 20260601_2 (Cơ sở 2), 20260602_4 (Cơ sở 2), 20260603_2 (Cơ sở 2), 20260613_3 (Cơ sở 2)</t>
         </is>
       </c>
       <c r="F61" t="n">
@@ -5359,7 +5359,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>20260604_3 (Cơ sở 2), 20260605_2 (Cơ sở 1), 20260605_3 (Cơ sở 1), 20260605_4 (Cơ sở 1), 20260608_1 (Cơ sở 2)</t>
+          <t>20260603_3 (Cơ sở 2), 20260604_2 (Cơ sở 2), 20260609_2 (Cơ sở 2), 20260611_3 (Cơ sở 2), 20260613_3 (Cơ sở 2)</t>
         </is>
       </c>
       <c r="F62" t="n">
@@ -5388,7 +5388,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>20260528_1 (Cơ sở 1), 20260605_2 (Cơ sở 1), 20260605_3 (Cơ sở 1), 20260610_3 (Cơ sở 1), 20260610_1 (Cơ sở 1), 20260610_2 (Cơ sở 1)</t>
+          <t>20260521_5 (Cơ sở 1), 20260522_5 (Cơ sở 1), 20260529_1 (Cơ sở 1), 20260605_2 (Cơ sở 1), 20260608_4 (Cơ sở 1), 20260613_3 (Cơ sở 1)</t>
         </is>
       </c>
       <c r="F63" t="n">
@@ -5413,11 +5413,11 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>20260530_2 (Cơ sở 1), 20260608_3 (Cơ sở 1), 20260608_4 (Cơ sở 1), 20260611_3 (Cơ sở 1), 20260611_1 (Cơ sở 1)</t>
+          <t>20260518_5 (Cơ sở 1), 20260519_5 (Cơ sở 1), 20260528_4 (Cơ sở 1), 20260602_5 (Cơ sở 1), 20260608_4 (Cơ sở 1), 20260612_2 (Cơ sở 1)</t>
         </is>
       </c>
       <c r="F64" t="n">
@@ -5442,11 +5442,11 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>20260521_5 (Cơ sở 1), 20260528_1 (Cơ sở 1), 20260528_2 (Cơ sở 1), 20260528_3 (Cơ sở 1), 20260528_4 (Cơ sở 1)</t>
+          <t>20260519_5 (Cơ sở 1), 20260528_2 (Cơ sở 1), 20260528_5 (Cơ sở 1), 20260605_4 (Cơ sở 1), 20260612_2 (Cơ sở 1), 20260611_1 (Cơ sở 1)</t>
         </is>
       </c>
       <c r="F65" t="n">
@@ -5475,7 +5475,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>20260601_5 (Cơ sở 1), 20260602_1 (Cơ sở 2), 20260604_2 (Cơ sở 2), 20260605_4 (Cơ sở 1), 20260608_1 (Cơ sở 2)</t>
+          <t>20260525_2 (Cơ sở 2), 20260528_3 (Cơ sở 2), 20260529_1 (Cơ sở 2), 20260602_4 (Cơ sở 2), 20260613_3 (Cơ sở 2)</t>
         </is>
       </c>
       <c r="F66" t="n">
@@ -5504,7 +5504,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>20260528_3 (Cơ sở 2), 20260609_2 (Cơ sở 2), 20260608_1 (Cơ sở 2), 20260608_3 (Cơ sở 2), 20260608_4 (Cơ sở 2)</t>
+          <t>20260601_4 (Cơ sở 2), 20260603_3 (Cơ sở 2), 20260604_2 (Cơ sở 2), 20260613_3 (Cơ sở 2), 20260609_4 (Cơ sở 2)</t>
         </is>
       </c>
       <c r="F67" t="n">
@@ -5533,7 +5533,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>20260531_3 (Cơ sở 1), 20260601_1 (Cơ sở 2), 20260601_2 (Cơ sở 2), 20260602_5 (Cơ sở 1), 20260603_1 (Cơ sở 2)</t>
+          <t>20260528_1 (Cơ sở 1), 20260528_4 (Cơ sở 1), 20260529_2 (Cơ sở 1), 20260608_3 (Cơ sở 1), 20260611_1 (Cơ sở 1)</t>
         </is>
       </c>
       <c r="F68" t="n">
@@ -5562,7 +5562,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>20260525_2 (Cơ sở 2), 20260601_5 (Cơ sở 1), 20260602_1 (Cơ sở 2), 20260605_4 (Cơ sở 1), 20260608_1 (Cơ sở 2)</t>
+          <t>20260528_3 (Cơ sở 2), 20260601_3 (Cơ sở 2), 20260609_2 (Cơ sở 2), 20260608_1 (Cơ sở 2), 20260608_4 (Cơ sở 2)</t>
         </is>
       </c>
       <c r="F69" t="n">
@@ -5587,11 +5587,11 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>20260518_5 (Cơ sở 1), 20260519_5 (Cơ sở 1), 20260521_5 (Cơ sở 1), 20260529_2 (Cơ sở 1), 20260530_3 (Cơ sở 1)</t>
+          <t>20260528_1 (Cơ sở 1), 20260529_3 (Cơ sở 1), 20260530_2 (Cơ sở 1), 20260601_5 (Cơ sở 1), 20260608_3 (Cơ sở 1), 20260613_3 (Cơ sở 1)</t>
         </is>
       </c>
       <c r="F70" t="n">
@@ -5620,7 +5620,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>20260527_5 (Cơ sở 1), 20260528_1 (Cơ sở 1), 20260530_2 (Cơ sở 1), 20260530_3 (Cơ sở 1), 20260531_2 (Cơ sở 1)</t>
+          <t>20260601_5 (Cơ sở 1), 20260604_2 (Cơ sở 1), 20260608_4 (Cơ sở 1), 20260611_3 (Cơ sở 1), 20260610_4 (Cơ sở 1)</t>
         </is>
       </c>
       <c r="F71" t="n">
@@ -5649,7 +5649,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>20260603_2 (Cơ sở 2), 20260613_2 (Cơ sở 2), 20260613_3 (Cơ sở 2), 20260612_3 (Cơ sở 2), 20260612_4 (Cơ sở 2)</t>
+          <t>20260603_1 (Cơ sở 2), 20260604_2 (Cơ sở 2), 20260609_2 (Cơ sở 2), 20260608_1 (Cơ sở 2), 20260608_4 (Cơ sở 2)</t>
         </is>
       </c>
       <c r="F72" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>20260608_2 (Cơ sở 1), 20260608_3 (Cơ sở 1), 20260608_4 (Cơ sở 1), 20260609_2 (Cơ sở 1), 20260613_3 (Cơ sở 1)</t>
+          <t>20260529_1 (Cơ sở 1), 20260601_5 (Cơ sở 1), 20260602_5 (Cơ sở 1), 20260608_3 (Cơ sở 1), 20260610_3 (Cơ sở 1)</t>
         </is>
       </c>
       <c r="F73" t="n">
@@ -5707,7 +5707,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>20260521_5 (Cơ sở 1), 20260522_5 (Cơ sở 1), 20260523_3 (Cơ sở 1), 20260525_2 (Cơ sở 2), 20260525_5 (Cơ sở 1)</t>
+          <t>20260518_5 (Cơ sở 1), 20260523_3 (Cơ sở 1), 20260601_5 (Cơ sở 1), 20260604_2 (Cơ sở 1), 20260605_3 (Cơ sở 1)</t>
         </is>
       </c>
       <c r="F74" t="n">
@@ -5801,7 +5801,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
